--- a/Detail.xlsx
+++ b/Detail.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ptptmn-my.sharepoint.com/personal/oki_muttaqin_pertamina_com/Documents/OMSU/PENGEMBANGAN SISTIM/APLIKASI INVENTORY/PERSIAPAN/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuhri\Documents\Aplikasi Pertamina\inv\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3658" documentId="8_{0AAD556E-D943-4122-ADAC-9D78F8943A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{534EF88C-A567-4DFE-BD5C-063874F2322A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="2" xr2:uid="{EA806CEA-1F84-4C21-AC7C-0D6B6BE33AC1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{EA806CEA-1F84-4C21-AC7C-0D6B6BE33AC1}"/>
   </bookViews>
   <sheets>
     <sheet name="DETAIL" sheetId="1" r:id="rId1"/>
@@ -5424,7 +5424,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="30" x14ac:knownFonts="1">
     <font>
@@ -6058,7 +6058,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6140,7 +6140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6468,27 +6468,270 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6501,105 +6744,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -6671,156 +6821,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6844,10 +6844,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7171,38 +7167,38 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A3:H102"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.90625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="4.6328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="4.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="33" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" style="3" customWidth="1"/>
-    <col min="6" max="7" width="8.7265625" style="3"/>
-    <col min="8" max="8" width="25.08984375" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="13.109375" style="3" customWidth="1"/>
+    <col min="6" max="7" width="8.77734375" style="3"/>
+    <col min="8" max="8" width="25.109375" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="182" t="s">
+      <c r="C3" s="232" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="182"/>
-    </row>
-    <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="232"/>
+    </row>
+    <row r="4" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="231" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="181"/>
-      <c r="D4" s="181"/>
-    </row>
-    <row r="5" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="231"/>
+      <c r="D4" s="231"/>
+    </row>
+    <row r="5" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>66</v>
       </c>
@@ -7210,7 +7206,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>67</v>
       </c>
@@ -7218,7 +7214,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>68</v>
       </c>
@@ -7226,7 +7222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
         <v>69</v>
       </c>
@@ -7234,7 +7230,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
         <v>70</v>
       </c>
@@ -7242,7 +7238,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
         <v>93</v>
       </c>
@@ -7250,7 +7246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
         <v>94</v>
       </c>
@@ -7258,7 +7254,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
         <v>95</v>
       </c>
@@ -7266,7 +7262,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
         <v>96</v>
       </c>
@@ -7274,18 +7270,18 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="181" t="s">
+      <c r="B15" s="231" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="181"/>
-      <c r="D15" s="181"/>
-    </row>
-    <row r="16" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="231"/>
+      <c r="D15" s="231"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="1" t="s">
         <v>66</v>
@@ -7297,7 +7293,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
       <c r="C17" s="1" t="s">
         <v>67</v>
@@ -7306,7 +7302,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="1" t="s">
         <v>68</v>
@@ -7315,7 +7311,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="C19" s="1" t="s">
         <v>69</v>
@@ -7324,7 +7320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20" s="1" t="s">
         <v>70</v>
@@ -7333,7 +7329,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="C21" s="1" t="s">
         <v>93</v>
@@ -7342,7 +7338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2"/>
       <c r="C22" s="1" t="s">
         <v>94</v>
@@ -7351,7 +7347,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2"/>
       <c r="C23" s="1" t="s">
         <v>95</v>
@@ -7360,7 +7356,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2"/>
       <c r="C24" s="1" t="s">
         <v>96</v>
@@ -7369,7 +7365,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2"/>
       <c r="C25" s="1" t="s">
         <v>97</v>
@@ -7378,7 +7374,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2"/>
       <c r="C26" s="1" t="s">
         <v>98</v>
@@ -7387,7 +7383,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
       <c r="C27" s="1" t="s">
         <v>99</v>
@@ -7396,7 +7392,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
         <v>100</v>
       </c>
@@ -7404,7 +7400,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="1" t="s">
         <v>101</v>
       </c>
@@ -7412,7 +7408,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
@@ -7420,7 +7416,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1" t="s">
         <v>103</v>
       </c>
@@ -7428,7 +7424,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
         <v>104</v>
       </c>
@@ -7436,18 +7432,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:4" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="181" t="s">
+      <c r="B34" s="231" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="181"/>
-      <c r="D34" s="181"/>
-    </row>
-    <row r="35" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C34" s="231"/>
+      <c r="D34" s="231"/>
+    </row>
+    <row r="35" spans="1:4" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="1" t="s">
         <v>66</v>
       </c>
@@ -7455,42 +7451,42 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D36" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D37" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D38" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D39" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D40" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D41" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D42" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
         <v>67</v>
       </c>
@@ -7498,37 +7494,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D45" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D46" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D47" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D48" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D49" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D50" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C52" s="1" t="s">
         <v>68</v>
       </c>
@@ -7536,17 +7532,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B54" s="181" t="s">
+      <c r="B54" s="231" t="s">
         <v>42</v>
       </c>
-      <c r="C54" s="181"/>
-      <c r="D54" s="181"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C54" s="231"/>
+      <c r="D54" s="231"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C55" s="1" t="s">
         <v>66</v>
       </c>
@@ -7554,7 +7550,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C56" s="1" t="s">
         <v>67</v>
       </c>
@@ -7562,7 +7558,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C57" s="1" t="s">
         <v>68</v>
       </c>
@@ -7570,7 +7566,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C58" s="1" t="s">
         <v>69</v>
       </c>
@@ -7578,7 +7574,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C59" s="1" t="s">
         <v>70</v>
       </c>
@@ -7586,17 +7582,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B61" s="181" t="s">
+      <c r="B61" s="231" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="181"/>
-      <c r="D61" s="181"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C61" s="231"/>
+      <c r="D61" s="231"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
         <v>66</v>
       </c>
@@ -7604,7 +7600,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C63" s="1" t="s">
         <v>67</v>
       </c>
@@ -7612,7 +7608,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
         <v>68</v>
       </c>
@@ -7620,7 +7616,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C65" s="1" t="s">
         <v>69</v>
       </c>
@@ -7628,7 +7624,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
         <v>70</v>
       </c>
@@ -7636,17 +7632,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B68" s="181" t="s">
+      <c r="B68" s="231" t="s">
         <v>60</v>
       </c>
-      <c r="C68" s="181"/>
-      <c r="D68" s="181"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C68" s="231"/>
+      <c r="D68" s="231"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C69" s="1" t="s">
         <v>66</v>
       </c>
@@ -7654,7 +7650,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
         <v>67</v>
       </c>
@@ -7662,7 +7658,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C71" s="1" t="s">
         <v>68</v>
       </c>
@@ -7670,7 +7666,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C72" s="1" t="s">
         <v>69</v>
       </c>
@@ -7678,17 +7674,17 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B74" s="181" t="s">
+      <c r="B74" s="231" t="s">
         <v>78</v>
       </c>
-      <c r="C74" s="181"/>
-      <c r="D74" s="181"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C74" s="231"/>
+      <c r="D74" s="231"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7696,7 +7692,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
@@ -7704,7 +7700,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7712,7 +7708,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
         <v>69</v>
       </c>
@@ -7720,7 +7716,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C79" s="1" t="s">
         <v>70</v>
       </c>
@@ -7728,7 +7724,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
         <v>93</v>
       </c>
@@ -7736,7 +7732,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C81" s="1" t="s">
         <v>94</v>
       </c>
@@ -7744,7 +7740,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C82" s="1" t="s">
         <v>95</v>
       </c>
@@ -7752,16 +7748,16 @@
         <v>86</v>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H99" s="27"/>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H100" s="27"/>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H101" s="27"/>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H102" s="27"/>
     </row>
   </sheetData>
@@ -7785,58 +7781,58 @@
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
-    <col min="2" max="2" width="3.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.453125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.90625" style="25" customWidth="1"/>
-    <col min="6" max="7" width="6.6328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.6328125" style="22" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.88671875" style="25" customWidth="1"/>
+    <col min="6" max="7" width="6.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.6640625" style="22" customWidth="1"/>
+    <col min="9" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="192" t="s">
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="242" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="244" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="195"/>
-      <c r="D4" s="198" t="s">
+      <c r="C4" s="245"/>
+      <c r="D4" s="248" t="s">
         <v>134</v>
       </c>
-      <c r="E4" s="200" t="s">
+      <c r="E4" s="250" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="183" t="s">
+      <c r="F4" s="233" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="184"/>
-      <c r="H4" s="185"/>
-    </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="193"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="201"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="235"/>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="243"/>
+      <c r="B5" s="246"/>
+      <c r="C5" s="247"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="251"/>
       <c r="F5" s="21" t="s">
         <v>127</v>
       </c>
@@ -7847,7 +7843,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -7869,7 +7865,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>2</v>
       </c>
@@ -7891,7 +7887,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -7913,7 +7909,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>4</v>
       </c>
@@ -7927,7 +7923,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="24"/>
     </row>
-    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -7949,7 +7945,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>6</v>
       </c>
@@ -7969,7 +7965,7 @@
       </c>
       <c r="H11" s="24"/>
     </row>
-    <row r="12" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -7989,7 +7985,7 @@
       </c>
       <c r="H12" s="24"/>
     </row>
-    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>8</v>
       </c>
@@ -7997,7 +7993,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="189" t="s">
+      <c r="D13" s="239" t="s">
         <v>119</v>
       </c>
       <c r="E13" s="26" t="s">
@@ -8009,7 +8005,7 @@
       </c>
       <c r="H13" s="24"/>
     </row>
-    <row r="14" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>66</v>
       </c>
@@ -8017,13 +8013,13 @@
         <v>71</v>
       </c>
       <c r="C14" s="12"/>
-      <c r="D14" s="190"/>
+      <c r="D14" s="240"/>
       <c r="E14" s="26"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="24"/>
     </row>
-    <row r="15" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>67</v>
       </c>
@@ -8031,13 +8027,13 @@
         <v>72</v>
       </c>
       <c r="C15" s="12"/>
-      <c r="D15" s="190"/>
+      <c r="D15" s="240"/>
       <c r="E15" s="26"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="24"/>
     </row>
-    <row r="16" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>68</v>
       </c>
@@ -8045,13 +8041,13 @@
         <v>73</v>
       </c>
       <c r="C16" s="12"/>
-      <c r="D16" s="190"/>
+      <c r="D16" s="240"/>
       <c r="E16" s="26"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="24"/>
     </row>
-    <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>69</v>
       </c>
@@ -8059,13 +8055,13 @@
         <v>74</v>
       </c>
       <c r="C17" s="12"/>
-      <c r="D17" s="190"/>
+      <c r="D17" s="240"/>
       <c r="E17" s="26"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="24"/>
     </row>
-    <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>70</v>
       </c>
@@ -8073,13 +8069,13 @@
         <v>75</v>
       </c>
       <c r="C18" s="12"/>
-      <c r="D18" s="191"/>
+      <c r="D18" s="241"/>
       <c r="E18" s="26"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="24"/>
     </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>9</v>
       </c>
@@ -8099,7 +8095,7 @@
       </c>
       <c r="H19" s="24"/>
     </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>10</v>
       </c>
@@ -8119,7 +8115,7 @@
       </c>
       <c r="H20" s="24"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>11</v>
       </c>
@@ -8127,10 +8123,10 @@
         <v>78</v>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="189" t="s">
+      <c r="D21" s="239" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="186" t="s">
+      <c r="E21" s="236" t="s">
         <v>141</v>
       </c>
       <c r="F21" s="10"/>
@@ -8139,7 +8135,7 @@
       </c>
       <c r="H21" s="24"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>66</v>
       </c>
@@ -8147,13 +8143,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="13"/>
-      <c r="D22" s="190"/>
-      <c r="E22" s="187"/>
+      <c r="D22" s="240"/>
+      <c r="E22" s="237"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="24"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="14" t="s">
         <v>110</v>
@@ -8161,13 +8157,13 @@
       <c r="C23" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="190"/>
-      <c r="E23" s="187"/>
+      <c r="D23" s="240"/>
+      <c r="E23" s="237"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="24"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="14" t="s">
         <v>110</v>
@@ -8175,13 +8171,13 @@
       <c r="C24" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="190"/>
-      <c r="E24" s="187"/>
+      <c r="D24" s="240"/>
+      <c r="E24" s="237"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="24"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="14" t="s">
         <v>110</v>
@@ -8189,13 +8185,13 @@
       <c r="C25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="190"/>
-      <c r="E25" s="187"/>
+      <c r="D25" s="240"/>
+      <c r="E25" s="237"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="24"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="14" t="s">
         <v>110</v>
@@ -8203,13 +8199,13 @@
       <c r="C26" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="190"/>
-      <c r="E26" s="187"/>
+      <c r="D26" s="240"/>
+      <c r="E26" s="237"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="24"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="14" t="s">
         <v>110</v>
@@ -8217,13 +8213,13 @@
       <c r="C27" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="190"/>
-      <c r="E27" s="187"/>
+      <c r="D27" s="240"/>
+      <c r="E27" s="237"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="24"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="14" t="s">
         <v>110</v>
@@ -8231,13 +8227,13 @@
       <c r="C28" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="190"/>
-      <c r="E28" s="187"/>
+      <c r="D28" s="240"/>
+      <c r="E28" s="237"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
       <c r="H28" s="24"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="14" t="s">
         <v>110</v>
@@ -8245,13 +8241,13 @@
       <c r="C29" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="190"/>
-      <c r="E29" s="187"/>
+      <c r="D29" s="240"/>
+      <c r="E29" s="237"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="24"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="14" t="s">
         <v>110</v>
@@ -8259,13 +8255,13 @@
       <c r="C30" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="190"/>
-      <c r="E30" s="187"/>
+      <c r="D30" s="240"/>
+      <c r="E30" s="237"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="24"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="14" t="s">
         <v>110</v>
@@ -8273,13 +8269,13 @@
       <c r="C31" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="190"/>
-      <c r="E31" s="187"/>
+      <c r="D31" s="240"/>
+      <c r="E31" s="237"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="24"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>67</v>
       </c>
@@ -8287,13 +8283,13 @@
         <v>24</v>
       </c>
       <c r="C32" s="17"/>
-      <c r="D32" s="190"/>
-      <c r="E32" s="187"/>
+      <c r="D32" s="240"/>
+      <c r="E32" s="237"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="24"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="14" t="s">
         <v>110</v>
@@ -8301,13 +8297,13 @@
       <c r="C33" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="190"/>
-      <c r="E33" s="187"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="237"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
       <c r="H33" s="24"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="14" t="s">
         <v>110</v>
@@ -8315,13 +8311,13 @@
       <c r="C34" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="190"/>
-      <c r="E34" s="187"/>
+      <c r="D34" s="240"/>
+      <c r="E34" s="237"/>
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
       <c r="H34" s="24"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="14" t="s">
         <v>110</v>
@@ -8329,13 +8325,13 @@
       <c r="C35" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="190"/>
-      <c r="E35" s="187"/>
+      <c r="D35" s="240"/>
+      <c r="E35" s="237"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="24"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="14" t="s">
         <v>110</v>
@@ -8343,13 +8339,13 @@
       <c r="C36" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="190"/>
-      <c r="E36" s="187"/>
+      <c r="D36" s="240"/>
+      <c r="E36" s="237"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
       <c r="H36" s="24"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="14" t="s">
         <v>110</v>
@@ -8357,13 +8353,13 @@
       <c r="C37" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="190"/>
-      <c r="E37" s="187"/>
+      <c r="D37" s="240"/>
+      <c r="E37" s="237"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="24"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="14" t="s">
         <v>110</v>
@@ -8371,13 +8367,13 @@
       <c r="C38" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="190"/>
-      <c r="E38" s="187"/>
+      <c r="D38" s="240"/>
+      <c r="E38" s="237"/>
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
       <c r="H38" s="24"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="14" t="s">
         <v>110</v>
@@ -8385,13 +8381,13 @@
       <c r="C39" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="190"/>
-      <c r="E39" s="187"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="237"/>
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
       <c r="H39" s="24"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="14" t="s">
         <v>110</v>
@@ -8399,13 +8395,13 @@
       <c r="C40" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="190"/>
-      <c r="E40" s="187"/>
+      <c r="D40" s="240"/>
+      <c r="E40" s="237"/>
       <c r="F40" s="10"/>
       <c r="G40" s="10"/>
       <c r="H40" s="24"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
       <c r="B41" s="14" t="s">
         <v>110</v>
@@ -8413,13 +8409,13 @@
       <c r="C41" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="190"/>
-      <c r="E41" s="187"/>
+      <c r="D41" s="240"/>
+      <c r="E41" s="237"/>
       <c r="F41" s="10"/>
       <c r="G41" s="10"/>
       <c r="H41" s="24"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="10"/>
       <c r="B42" s="14" t="s">
         <v>110</v>
@@ -8427,13 +8423,13 @@
       <c r="C42" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="190"/>
-      <c r="E42" s="187"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="237"/>
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
       <c r="H42" s="24"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
       <c r="B43" s="14" t="s">
         <v>110</v>
@@ -8441,13 +8437,13 @@
       <c r="C43" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="190"/>
-      <c r="E43" s="187"/>
+      <c r="D43" s="240"/>
+      <c r="E43" s="237"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
       <c r="H43" s="24"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
       <c r="B44" s="14" t="s">
         <v>110</v>
@@ -8455,13 +8451,13 @@
       <c r="C44" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="190"/>
-      <c r="E44" s="187"/>
+      <c r="D44" s="240"/>
+      <c r="E44" s="237"/>
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
       <c r="H44" s="24"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
       <c r="B45" s="14" t="s">
         <v>110</v>
@@ -8469,13 +8465,13 @@
       <c r="C45" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="190"/>
-      <c r="E45" s="187"/>
+      <c r="D45" s="240"/>
+      <c r="E45" s="237"/>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
       <c r="H45" s="24"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="14" t="s">
         <v>110</v>
@@ -8483,13 +8479,13 @@
       <c r="C46" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="190"/>
-      <c r="E46" s="187"/>
+      <c r="D46" s="240"/>
+      <c r="E46" s="237"/>
       <c r="F46" s="10"/>
       <c r="G46" s="10"/>
       <c r="H46" s="24"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="14" t="s">
         <v>110</v>
@@ -8497,13 +8493,13 @@
       <c r="C47" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="190"/>
-      <c r="E47" s="187"/>
+      <c r="D47" s="240"/>
+      <c r="E47" s="237"/>
       <c r="F47" s="10"/>
       <c r="G47" s="10"/>
       <c r="H47" s="24"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="14" t="s">
         <v>110</v>
@@ -8511,13 +8507,13 @@
       <c r="C48" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="190"/>
-      <c r="E48" s="187"/>
+      <c r="D48" s="240"/>
+      <c r="E48" s="237"/>
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
       <c r="H48" s="24"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
       <c r="B49" s="14" t="s">
         <v>110</v>
@@ -8525,13 +8521,13 @@
       <c r="C49" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="190"/>
-      <c r="E49" s="187"/>
+      <c r="D49" s="240"/>
+      <c r="E49" s="237"/>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
       <c r="H49" s="24"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>68</v>
       </c>
@@ -8539,205 +8535,205 @@
         <v>114</v>
       </c>
       <c r="C50" s="15"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="187"/>
+      <c r="D50" s="240"/>
+      <c r="E50" s="237"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="24"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="14"/>
       <c r="C51" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D51" s="190"/>
-      <c r="E51" s="187"/>
+      <c r="D51" s="240"/>
+      <c r="E51" s="237"/>
       <c r="F51" s="10"/>
       <c r="G51" s="10"/>
       <c r="H51" s="24"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="14"/>
       <c r="C52" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="190"/>
-      <c r="E52" s="187"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="237"/>
       <c r="F52" s="10"/>
       <c r="G52" s="10"/>
       <c r="H52" s="24"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="14"/>
       <c r="C53" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D53" s="190"/>
-      <c r="E53" s="187"/>
+      <c r="D53" s="240"/>
+      <c r="E53" s="237"/>
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="24"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="14"/>
       <c r="C54" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="190"/>
-      <c r="E54" s="187"/>
+      <c r="D54" s="240"/>
+      <c r="E54" s="237"/>
       <c r="F54" s="10"/>
       <c r="G54" s="10"/>
       <c r="H54" s="24"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="14"/>
       <c r="C55" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="190"/>
-      <c r="E55" s="187"/>
+      <c r="D55" s="240"/>
+      <c r="E55" s="237"/>
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
       <c r="H55" s="24"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="14"/>
       <c r="C56" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D56" s="190"/>
-      <c r="E56" s="187"/>
+      <c r="D56" s="240"/>
+      <c r="E56" s="237"/>
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
       <c r="H56" s="24"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="14"/>
       <c r="C57" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D57" s="190"/>
-      <c r="E57" s="187"/>
+      <c r="D57" s="240"/>
+      <c r="E57" s="237"/>
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>
       <c r="H57" s="24"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="14"/>
       <c r="C58" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="190"/>
-      <c r="E58" s="187"/>
+      <c r="D58" s="240"/>
+      <c r="E58" s="237"/>
       <c r="F58" s="10"/>
       <c r="G58" s="10"/>
       <c r="H58" s="24"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="14"/>
       <c r="C59" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D59" s="190"/>
-      <c r="E59" s="187"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="237"/>
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
       <c r="H59" s="24"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="14"/>
       <c r="C60" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="190"/>
-      <c r="E60" s="187"/>
+      <c r="D60" s="240"/>
+      <c r="E60" s="237"/>
       <c r="F60" s="10"/>
       <c r="G60" s="10"/>
       <c r="H60" s="24"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="14"/>
       <c r="C61" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="190"/>
-      <c r="E61" s="187"/>
+      <c r="D61" s="240"/>
+      <c r="E61" s="237"/>
       <c r="F61" s="10"/>
       <c r="G61" s="10"/>
       <c r="H61" s="24"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="14"/>
       <c r="C62" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D62" s="190"/>
-      <c r="E62" s="187"/>
+      <c r="D62" s="240"/>
+      <c r="E62" s="237"/>
       <c r="F62" s="10"/>
       <c r="G62" s="10"/>
       <c r="H62" s="24"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="14"/>
       <c r="C63" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="190"/>
-      <c r="E63" s="187"/>
+      <c r="D63" s="240"/>
+      <c r="E63" s="237"/>
       <c r="F63" s="10"/>
       <c r="G63" s="10"/>
       <c r="H63" s="24"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="14"/>
       <c r="C64" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="190"/>
-      <c r="E64" s="187"/>
+      <c r="D64" s="240"/>
+      <c r="E64" s="237"/>
       <c r="F64" s="10"/>
       <c r="G64" s="10"/>
       <c r="H64" s="24"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="14"/>
       <c r="C65" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="190"/>
-      <c r="E65" s="187"/>
+      <c r="D65" s="240"/>
+      <c r="E65" s="237"/>
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
       <c r="H65" s="24"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="14"/>
       <c r="C66" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D66" s="190"/>
-      <c r="E66" s="187"/>
+      <c r="D66" s="240"/>
+      <c r="E66" s="237"/>
       <c r="F66" s="10"/>
       <c r="G66" s="10"/>
       <c r="H66" s="24"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
         <v>69</v>
       </c>
@@ -8745,13 +8741,13 @@
         <v>42</v>
       </c>
       <c r="C67" s="17"/>
-      <c r="D67" s="190"/>
-      <c r="E67" s="187"/>
+      <c r="D67" s="240"/>
+      <c r="E67" s="237"/>
       <c r="F67" s="10"/>
       <c r="G67" s="10"/>
       <c r="H67" s="24"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="14" t="s">
         <v>110</v>
@@ -8759,13 +8755,13 @@
       <c r="C68" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="190"/>
-      <c r="E68" s="187"/>
+      <c r="D68" s="240"/>
+      <c r="E68" s="237"/>
       <c r="F68" s="10"/>
       <c r="G68" s="10"/>
       <c r="H68" s="24"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="14" t="s">
         <v>110</v>
@@ -8773,13 +8769,13 @@
       <c r="C69" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D69" s="190"/>
-      <c r="E69" s="187"/>
+      <c r="D69" s="240"/>
+      <c r="E69" s="237"/>
       <c r="F69" s="10"/>
       <c r="G69" s="10"/>
       <c r="H69" s="24"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="14" t="s">
         <v>110</v>
@@ -8787,13 +8783,13 @@
       <c r="C70" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D70" s="190"/>
-      <c r="E70" s="187"/>
+      <c r="D70" s="240"/>
+      <c r="E70" s="237"/>
       <c r="F70" s="10"/>
       <c r="G70" s="10"/>
       <c r="H70" s="24"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="14" t="s">
         <v>110</v>
@@ -8801,13 +8797,13 @@
       <c r="C71" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D71" s="190"/>
-      <c r="E71" s="187"/>
+      <c r="D71" s="240"/>
+      <c r="E71" s="237"/>
       <c r="F71" s="10"/>
       <c r="G71" s="10"/>
       <c r="H71" s="24"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="14" t="s">
         <v>110</v>
@@ -8815,13 +8811,13 @@
       <c r="C72" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="190"/>
-      <c r="E72" s="187"/>
+      <c r="D72" s="240"/>
+      <c r="E72" s="237"/>
       <c r="F72" s="10"/>
       <c r="G72" s="10"/>
       <c r="H72" s="24"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
         <v>70</v>
       </c>
@@ -8829,13 +8825,13 @@
         <v>50</v>
       </c>
       <c r="C73" s="17"/>
-      <c r="D73" s="190"/>
-      <c r="E73" s="187"/>
+      <c r="D73" s="240"/>
+      <c r="E73" s="237"/>
       <c r="F73" s="10"/>
       <c r="G73" s="10"/>
       <c r="H73" s="24"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="14" t="s">
         <v>110</v>
@@ -8843,13 +8839,13 @@
       <c r="C74" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D74" s="190"/>
-      <c r="E74" s="187"/>
+      <c r="D74" s="240"/>
+      <c r="E74" s="237"/>
       <c r="F74" s="10"/>
       <c r="G74" s="10"/>
       <c r="H74" s="24"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="14" t="s">
         <v>110</v>
@@ -8857,13 +8853,13 @@
       <c r="C75" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D75" s="190"/>
-      <c r="E75" s="187"/>
+      <c r="D75" s="240"/>
+      <c r="E75" s="237"/>
       <c r="F75" s="10"/>
       <c r="G75" s="10"/>
       <c r="H75" s="24"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="14" t="s">
         <v>110</v>
@@ -8871,13 +8867,13 @@
       <c r="C76" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D76" s="190"/>
-      <c r="E76" s="187"/>
+      <c r="D76" s="240"/>
+      <c r="E76" s="237"/>
       <c r="F76" s="10"/>
       <c r="G76" s="10"/>
       <c r="H76" s="24"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="14" t="s">
         <v>110</v>
@@ -8885,13 +8881,13 @@
       <c r="C77" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D77" s="190"/>
-      <c r="E77" s="187"/>
+      <c r="D77" s="240"/>
+      <c r="E77" s="237"/>
       <c r="F77" s="10"/>
       <c r="G77" s="10"/>
       <c r="H77" s="24"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="14" t="s">
         <v>110</v>
@@ -8899,13 +8895,13 @@
       <c r="C78" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D78" s="190"/>
-      <c r="E78" s="187"/>
+      <c r="D78" s="240"/>
+      <c r="E78" s="237"/>
       <c r="F78" s="10"/>
       <c r="G78" s="10"/>
       <c r="H78" s="24"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>93</v>
       </c>
@@ -8913,13 +8909,13 @@
         <v>79</v>
       </c>
       <c r="C79" s="17"/>
-      <c r="D79" s="190"/>
-      <c r="E79" s="187"/>
+      <c r="D79" s="240"/>
+      <c r="E79" s="237"/>
       <c r="F79" s="10"/>
       <c r="G79" s="10"/>
       <c r="H79" s="24"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
         <v>94</v>
       </c>
@@ -8927,13 +8923,13 @@
         <v>112</v>
       </c>
       <c r="C80" s="17"/>
-      <c r="D80" s="190"/>
-      <c r="E80" s="187"/>
+      <c r="D80" s="240"/>
+      <c r="E80" s="237"/>
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
       <c r="H80" s="24"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
         <v>95</v>
       </c>
@@ -8941,8 +8937,8 @@
         <v>113</v>
       </c>
       <c r="C81" s="17"/>
-      <c r="D81" s="191"/>
-      <c r="E81" s="188"/>
+      <c r="D81" s="241"/>
+      <c r="E81" s="238"/>
       <c r="F81" s="10"/>
       <c r="G81" s="10"/>
       <c r="H81" s="24"/>
@@ -8968,52 +8964,52 @@
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:M297"/>
-  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.90625" style="249" customWidth="1"/>
-    <col min="2" max="2" width="16" style="207" customWidth="1"/>
-    <col min="3" max="3" width="18" style="207" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" style="207" customWidth="1"/>
-    <col min="5" max="5" width="35.453125" style="25" customWidth="1"/>
-    <col min="6" max="6" width="3.54296875" style="54" customWidth="1"/>
-    <col min="7" max="7" width="40.08984375" style="36" customWidth="1"/>
-    <col min="8" max="9" width="34.08984375" style="36" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="181" customWidth="1"/>
+    <col min="2" max="2" width="16" style="139" customWidth="1"/>
+    <col min="3" max="3" width="18" style="139" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="139" customWidth="1"/>
+    <col min="5" max="5" width="35.44140625" style="25" customWidth="1"/>
+    <col min="6" max="6" width="3.5546875" style="54" customWidth="1"/>
+    <col min="7" max="7" width="40.109375" style="36" customWidth="1"/>
+    <col min="8" max="9" width="34.109375" style="36" customWidth="1"/>
     <col min="10" max="10" width="51" style="36" customWidth="1"/>
-    <col min="11" max="11" width="1.26953125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="4.7265625" style="109" customWidth="1"/>
-    <col min="13" max="16384" width="8.7265625" style="3"/>
+    <col min="11" max="11" width="1.21875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="4.77734375" style="109" customWidth="1"/>
+    <col min="13" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="250" t="s">
+    <row r="1" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="182" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="20" x14ac:dyDescent="0.35">
-      <c r="A2" s="250" t="s">
+    <row r="2" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="182" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="208" t="s">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="141" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="141" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="209" t="s">
+      <c r="D4" s="141" t="s">
         <v>143</v>
       </c>
       <c r="E4" s="84" t="s">
         <v>578</v>
       </c>
-      <c r="F4" s="158" t="s">
+      <c r="F4" s="209" t="s">
         <v>577</v>
       </c>
-      <c r="G4" s="159"/>
+      <c r="G4" s="210"/>
       <c r="H4" s="84" t="s">
         <v>280</v>
       </c>
@@ -9025,20 +9021,20 @@
       </c>
       <c r="L4" s="109"/>
     </row>
-    <row r="5" spans="1:12" s="38" customFormat="1" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="210"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
+    <row r="5" spans="1:12" s="38" customFormat="1" ht="8.5500000000000007" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="142"/>
+      <c r="B5" s="143"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
       <c r="E5" s="37"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="163"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="214"/>
       <c r="H5" s="74"/>
       <c r="I5" s="74"/>
       <c r="J5" s="74"/>
       <c r="L5" s="110"/>
     </row>
-    <row r="6" spans="1:12" s="83" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" s="83" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="80" t="s">
         <v>182</v>
       </c>
@@ -9046,57 +9042,57 @@
       <c r="C6" s="81"/>
       <c r="D6" s="81"/>
       <c r="E6" s="81"/>
-      <c r="F6" s="160" t="s">
+      <c r="F6" s="211" t="s">
         <v>286</v>
       </c>
-      <c r="G6" s="161"/>
+      <c r="G6" s="212"/>
       <c r="H6" s="82"/>
       <c r="I6" s="82"/>
       <c r="J6" s="82"/>
       <c r="L6" s="107"/>
     </row>
-    <row r="7" spans="1:12" s="44" customFormat="1" ht="9.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="212"/>
-      <c r="B7" s="213"/>
-      <c r="C7" s="213"/>
-      <c r="D7" s="213"/>
+    <row r="7" spans="1:12" s="44" customFormat="1" ht="9.4499999999999993" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="144"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145"/>
       <c r="E7" s="43"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="165"/>
+      <c r="F7" s="215"/>
+      <c r="G7" s="216"/>
       <c r="H7" s="75"/>
       <c r="I7" s="75"/>
       <c r="J7" s="75"/>
       <c r="L7" s="111"/>
     </row>
-    <row r="8" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="205">
+    <row r="8" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="137">
         <v>1</v>
       </c>
-      <c r="B8" s="206" t="s">
+      <c r="B8" s="138" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="206" t="s">
+      <c r="C8" s="138" t="s">
         <v>568</v>
       </c>
-      <c r="D8" s="206" t="s">
+      <c r="D8" s="138" t="s">
         <v>142</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="F8" s="142" t="s">
+      <c r="F8" s="193" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="143"/>
+      <c r="G8" s="194"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:12" s="25" customFormat="1" ht="89" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="214"/>
-      <c r="B9" s="214"/>
-      <c r="C9" s="214"/>
-      <c r="D9" s="214"/>
+    <row r="9" spans="1:12" s="25" customFormat="1" ht="88.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="146"/>
+      <c r="B9" s="146"/>
+      <c r="C9" s="146"/>
+      <c r="D9" s="146"/>
       <c r="E9" s="28"/>
       <c r="F9" s="58" t="s">
         <v>66</v>
@@ -9115,11 +9111,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="215"/>
-      <c r="B10" s="214"/>
-      <c r="C10" s="214"/>
-      <c r="D10" s="214"/>
+    <row r="10" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="147"/>
+      <c r="B10" s="146"/>
+      <c r="C10" s="146"/>
+      <c r="D10" s="146"/>
       <c r="E10" s="28"/>
       <c r="F10" s="58" t="s">
         <v>67</v>
@@ -9140,11 +9136,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="215"/>
-      <c r="B11" s="214"/>
-      <c r="C11" s="214"/>
-      <c r="D11" s="214"/>
+    <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="147"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
       <c r="E11" s="28"/>
       <c r="F11" s="58" t="s">
         <v>68</v>
@@ -9165,11 +9161,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="215"/>
-      <c r="B12" s="214"/>
-      <c r="C12" s="214"/>
-      <c r="D12" s="214"/>
+    <row r="12" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="147"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="146"/>
       <c r="E12" s="28"/>
       <c r="F12" s="58" t="s">
         <v>69</v>
@@ -9190,11 +9186,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="333.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="215"/>
-      <c r="B13" s="214"/>
-      <c r="C13" s="214"/>
-      <c r="D13" s="214"/>
+    <row r="13" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="147"/>
+      <c r="B13" s="146"/>
+      <c r="C13" s="146"/>
+      <c r="D13" s="146"/>
       <c r="E13" s="28"/>
       <c r="F13" s="58" t="s">
         <v>70</v>
@@ -9215,11 +9211,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A14" s="215"/>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
+    <row r="14" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="147"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
       <c r="E14" s="28"/>
       <c r="F14" s="58" t="s">
         <v>93</v>
@@ -9238,11 +9234,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="215"/>
-      <c r="B15" s="214"/>
-      <c r="C15" s="214"/>
-      <c r="D15" s="214"/>
+    <row r="15" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="147"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="146"/>
       <c r="E15" s="28"/>
       <c r="F15" s="58" t="s">
         <v>94</v>
@@ -9261,11 +9257,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="215"/>
-      <c r="B16" s="214"/>
-      <c r="C16" s="214"/>
-      <c r="D16" s="214"/>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="147"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
       <c r="E16" s="28"/>
       <c r="F16" s="100"/>
       <c r="G16" s="101"/>
@@ -9273,11 +9269,11 @@
       <c r="I16" s="71"/>
       <c r="J16" s="71"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="215"/>
-      <c r="B17" s="214"/>
-      <c r="C17" s="214"/>
-      <c r="D17" s="214"/>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="147"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="146"/>
       <c r="E17" s="28"/>
       <c r="F17" s="117"/>
       <c r="G17" s="126" t="s">
@@ -9287,11 +9283,11 @@
       <c r="I17" s="40"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="215"/>
-      <c r="B18" s="214"/>
-      <c r="C18" s="214"/>
-      <c r="D18" s="214"/>
+    <row r="18" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="147"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="146"/>
       <c r="E18" s="28"/>
       <c r="F18" s="58" t="s">
         <v>66</v>
@@ -9302,7 +9298,7 @@
       <c r="H18" s="33" t="s">
         <v>426</v>
       </c>
-      <c r="I18" s="139" t="s">
+      <c r="I18" s="198" t="s">
         <v>565</v>
       </c>
       <c r="J18" s="33" t="s">
@@ -9312,11 +9308,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="215"/>
-      <c r="B19" s="214"/>
-      <c r="C19" s="214"/>
-      <c r="D19" s="214"/>
+    <row r="19" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="147"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="146"/>
       <c r="E19" s="28"/>
       <c r="F19" s="58" t="s">
         <v>67</v>
@@ -9327,7 +9323,7 @@
       <c r="H19" s="33" t="s">
         <v>563</v>
       </c>
-      <c r="I19" s="140"/>
+      <c r="I19" s="224"/>
       <c r="J19" s="33" t="s">
         <v>478</v>
       </c>
@@ -9335,11 +9331,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="215"/>
-      <c r="B20" s="214"/>
-      <c r="C20" s="214"/>
-      <c r="D20" s="214"/>
+    <row r="20" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="147"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="146"/>
+      <c r="D20" s="146"/>
       <c r="E20" s="28"/>
       <c r="F20" s="58" t="s">
         <v>68</v>
@@ -9350,7 +9346,7 @@
       <c r="H20" s="33" t="s">
         <v>427</v>
       </c>
-      <c r="I20" s="140"/>
+      <c r="I20" s="224"/>
       <c r="J20" s="33" t="s">
         <v>283</v>
       </c>
@@ -9358,11 +9354,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="215"/>
-      <c r="B21" s="214"/>
-      <c r="C21" s="214"/>
-      <c r="D21" s="214"/>
+    <row r="21" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="147"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="146"/>
       <c r="E21" s="28"/>
       <c r="F21" s="58" t="s">
         <v>69</v>
@@ -9373,7 +9369,7 @@
       <c r="H21" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="I21" s="141"/>
+      <c r="I21" s="199"/>
       <c r="J21" s="33" t="s">
         <v>284</v>
       </c>
@@ -9381,11 +9377,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="215"/>
-      <c r="B22" s="214"/>
-      <c r="C22" s="214"/>
-      <c r="D22" s="214"/>
+    <row r="22" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="147"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="146"/>
       <c r="E22" s="28"/>
       <c r="F22" s="58" t="s">
         <v>70</v>
@@ -9404,11 +9400,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="215"/>
-      <c r="B23" s="214"/>
-      <c r="C23" s="214"/>
-      <c r="D23" s="214"/>
+    <row r="23" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="147"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
       <c r="E23" s="28"/>
       <c r="F23" s="58" t="s">
         <v>308</v>
@@ -9419,7 +9415,7 @@
       <c r="H23" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="I23" s="139" t="s">
+      <c r="I23" s="198" t="s">
         <v>564</v>
       </c>
       <c r="J23" s="33" t="s">
@@ -9429,11 +9425,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A24" s="215"/>
-      <c r="B24" s="214"/>
-      <c r="C24" s="214"/>
-      <c r="D24" s="214"/>
+    <row r="24" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="147"/>
+      <c r="B24" s="146"/>
+      <c r="C24" s="146"/>
+      <c r="D24" s="146"/>
       <c r="E24" s="28"/>
       <c r="F24" s="58" t="s">
         <v>309</v>
@@ -9444,7 +9440,7 @@
       <c r="H24" s="71" t="s">
         <v>338</v>
       </c>
-      <c r="I24" s="141"/>
+      <c r="I24" s="199"/>
       <c r="J24" s="33" t="s">
         <v>296</v>
       </c>
@@ -9452,11 +9448,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="215"/>
-      <c r="B25" s="214"/>
-      <c r="C25" s="214"/>
-      <c r="D25" s="214"/>
+    <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="147"/>
+      <c r="B25" s="146"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="146"/>
       <c r="E25" s="28"/>
       <c r="F25" s="58" t="s">
         <v>310</v>
@@ -9477,11 +9473,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="216"/>
-      <c r="B26" s="217"/>
-      <c r="C26" s="217"/>
-      <c r="D26" s="217"/>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="148"/>
+      <c r="B26" s="149"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
       <c r="E26" s="34"/>
       <c r="F26" s="56"/>
       <c r="G26" s="52"/>
@@ -9489,11 +9485,11 @@
       <c r="I26" s="76"/>
       <c r="J26" s="76"/>
     </row>
-    <row r="27" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="215"/>
-      <c r="B27" s="214"/>
-      <c r="C27" s="214"/>
-      <c r="D27" s="214"/>
+    <row r="27" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="147"/>
+      <c r="B27" s="146"/>
+      <c r="C27" s="146"/>
+      <c r="D27" s="146"/>
       <c r="E27" s="28"/>
       <c r="F27" s="95"/>
       <c r="G27" s="51"/>
@@ -9501,17 +9497,17 @@
       <c r="I27" s="77"/>
       <c r="J27" s="77"/>
     </row>
-    <row r="28" spans="1:12" s="39" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="205">
+    <row r="28" spans="1:12" s="39" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="137">
         <v>2</v>
       </c>
-      <c r="B28" s="206" t="s">
+      <c r="B28" s="138" t="s">
         <v>445</v>
       </c>
-      <c r="C28" s="206" t="s">
+      <c r="C28" s="138" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="206" t="s">
+      <c r="D28" s="138" t="s">
         <v>142</v>
       </c>
       <c r="E28" s="32" t="s">
@@ -9526,11 +9522,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A29" s="215"/>
-      <c r="B29" s="214"/>
-      <c r="C29" s="214"/>
-      <c r="D29" s="214"/>
+    <row r="29" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="147"/>
+      <c r="B29" s="146"/>
+      <c r="C29" s="146"/>
+      <c r="D29" s="146"/>
       <c r="E29" s="28"/>
       <c r="F29" s="58" t="s">
         <v>311</v>
@@ -9551,11 +9547,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A30" s="215"/>
-      <c r="B30" s="214"/>
-      <c r="C30" s="214"/>
-      <c r="D30" s="214"/>
+    <row r="30" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="147"/>
+      <c r="B30" s="146"/>
+      <c r="C30" s="146"/>
+      <c r="D30" s="146"/>
       <c r="E30" s="28"/>
       <c r="F30" s="113"/>
       <c r="G30" s="49"/>
@@ -9566,56 +9562,56 @@
       <c r="J30" s="33"/>
       <c r="L30" s="131"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="215"/>
-      <c r="B31" s="214"/>
-      <c r="C31" s="214"/>
-      <c r="D31" s="214"/>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="147"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="146"/>
       <c r="E31" s="28"/>
       <c r="F31" s="113"/>
       <c r="G31" s="49"/>
       <c r="H31" s="33"/>
-      <c r="I31" s="253" t="s">
+      <c r="I31" s="185" t="s">
         <v>579</v>
       </c>
       <c r="J31" s="33"/>
       <c r="L31" s="131"/>
     </row>
-    <row r="32" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A32" s="215"/>
-      <c r="B32" s="214"/>
-      <c r="C32" s="214"/>
-      <c r="D32" s="214"/>
+    <row r="32" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="147"/>
+      <c r="B32" s="146"/>
+      <c r="C32" s="146"/>
+      <c r="D32" s="146"/>
       <c r="E32" s="28"/>
       <c r="F32" s="113"/>
       <c r="G32" s="49"/>
       <c r="H32" s="33"/>
-      <c r="I32" s="251" t="s">
+      <c r="I32" s="183" t="s">
         <v>580</v>
       </c>
       <c r="J32" s="33"/>
       <c r="L32" s="131"/>
     </row>
-    <row r="33" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="215"/>
-      <c r="B33" s="214"/>
-      <c r="C33" s="214"/>
-      <c r="D33" s="214"/>
+    <row r="33" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="147"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="146"/>
+      <c r="D33" s="146"/>
       <c r="E33" s="28"/>
       <c r="F33" s="113"/>
       <c r="G33" s="49"/>
       <c r="H33" s="33"/>
-      <c r="I33" s="251" t="s">
+      <c r="I33" s="183" t="s">
         <v>581</v>
       </c>
       <c r="J33" s="33"/>
       <c r="L33" s="131"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="216"/>
-      <c r="B34" s="217"/>
-      <c r="C34" s="217"/>
-      <c r="D34" s="217"/>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="148"/>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="149"/>
       <c r="E34" s="34"/>
       <c r="F34" s="56"/>
       <c r="G34" s="52"/>
@@ -9623,11 +9619,11 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:12" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="215"/>
-      <c r="B35" s="214"/>
-      <c r="C35" s="214"/>
-      <c r="D35" s="214"/>
+    <row r="35" spans="1:12" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="147"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="146"/>
       <c r="E35" s="28"/>
       <c r="F35" s="57"/>
       <c r="G35" s="51"/>
@@ -9635,34 +9631,34 @@
       <c r="I35" s="32"/>
       <c r="J35" s="32"/>
     </row>
-    <row r="36" spans="1:12" s="39" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="205">
+    <row r="36" spans="1:12" s="39" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="137">
         <v>3</v>
       </c>
-      <c r="B36" s="206" t="s">
+      <c r="B36" s="138" t="s">
         <v>444</v>
       </c>
-      <c r="C36" s="206" t="s">
+      <c r="C36" s="138" t="s">
         <v>569</v>
       </c>
-      <c r="D36" s="206" t="s">
+      <c r="D36" s="138" t="s">
         <v>570</v>
       </c>
       <c r="E36" s="32" t="s">
         <v>479</v>
       </c>
-      <c r="F36" s="142"/>
-      <c r="G36" s="143"/>
+      <c r="F36" s="193"/>
+      <c r="G36" s="194"/>
       <c r="H36" s="32"/>
       <c r="I36" s="40"/>
       <c r="J36" s="40"/>
       <c r="L36" s="109"/>
     </row>
-    <row r="37" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A37" s="215"/>
-      <c r="B37" s="214"/>
-      <c r="C37" s="214"/>
-      <c r="D37" s="214"/>
+    <row r="37" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="147"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="146"/>
+      <c r="D37" s="146"/>
       <c r="E37" s="28"/>
       <c r="F37" s="58" t="s">
         <v>66</v>
@@ -9683,11 +9679,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A38" s="215"/>
-      <c r="B38" s="214"/>
-      <c r="C38" s="214"/>
-      <c r="D38" s="214"/>
+    <row r="38" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="147"/>
+      <c r="B38" s="146"/>
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
       <c r="E38" s="28"/>
       <c r="F38" s="58" t="s">
         <v>67</v>
@@ -9708,11 +9704,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="215"/>
-      <c r="B39" s="214"/>
-      <c r="C39" s="214"/>
-      <c r="D39" s="214"/>
+    <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="147"/>
+      <c r="B39" s="146"/>
+      <c r="C39" s="146"/>
+      <c r="D39" s="146"/>
       <c r="E39" s="28"/>
       <c r="F39" s="58" t="s">
         <v>68</v>
@@ -9731,11 +9727,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="215"/>
-      <c r="B40" s="214"/>
-      <c r="C40" s="214"/>
-      <c r="D40" s="214"/>
+    <row r="40" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="147"/>
+      <c r="B40" s="146"/>
+      <c r="C40" s="146"/>
+      <c r="D40" s="146"/>
       <c r="E40" s="28"/>
       <c r="F40" s="58" t="s">
         <v>69</v>
@@ -9754,11 +9750,11 @@
       </c>
       <c r="L40" s="131"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41" s="215"/>
-      <c r="B41" s="214"/>
-      <c r="C41" s="214"/>
-      <c r="D41" s="214"/>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="147"/>
+      <c r="B41" s="146"/>
+      <c r="C41" s="146"/>
+      <c r="D41" s="146"/>
       <c r="E41" s="28"/>
       <c r="F41" s="113"/>
       <c r="G41" s="49"/>
@@ -9767,56 +9763,56 @@
       <c r="J41" s="71"/>
       <c r="L41" s="131"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" s="215"/>
-      <c r="B42" s="214"/>
-      <c r="C42" s="214"/>
-      <c r="D42" s="214"/>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="147"/>
+      <c r="B42" s="146"/>
+      <c r="C42" s="146"/>
+      <c r="D42" s="146"/>
       <c r="E42" s="28"/>
       <c r="F42" s="113"/>
       <c r="G42" s="49"/>
       <c r="H42" s="71"/>
-      <c r="I42" s="252" t="s">
+      <c r="I42" s="184" t="s">
         <v>582</v>
       </c>
       <c r="J42" s="71"/>
       <c r="L42" s="131"/>
     </row>
-    <row r="43" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A43" s="215"/>
-      <c r="B43" s="214"/>
-      <c r="C43" s="214"/>
-      <c r="D43" s="214"/>
+    <row r="43" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="147"/>
+      <c r="B43" s="146"/>
+      <c r="C43" s="146"/>
+      <c r="D43" s="146"/>
       <c r="E43" s="28"/>
       <c r="F43" s="113"/>
       <c r="G43" s="49"/>
       <c r="H43" s="71"/>
-      <c r="I43" s="251" t="s">
+      <c r="I43" s="183" t="s">
         <v>583</v>
       </c>
       <c r="J43" s="71"/>
       <c r="L43" s="131"/>
     </row>
-    <row r="44" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A44" s="215"/>
-      <c r="B44" s="214"/>
-      <c r="C44" s="214"/>
-      <c r="D44" s="214"/>
+    <row r="44" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="147"/>
+      <c r="B44" s="146"/>
+      <c r="C44" s="146"/>
+      <c r="D44" s="146"/>
       <c r="E44" s="28"/>
       <c r="F44" s="113"/>
       <c r="G44" s="49"/>
       <c r="H44" s="71"/>
-      <c r="I44" s="251" t="s">
+      <c r="I44" s="183" t="s">
         <v>584</v>
       </c>
       <c r="J44" s="71"/>
       <c r="L44" s="131"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45" s="215"/>
-      <c r="B45" s="214"/>
-      <c r="C45" s="214"/>
-      <c r="D45" s="214"/>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="147"/>
+      <c r="B45" s="146"/>
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
       <c r="E45" s="28"/>
       <c r="F45" s="113"/>
       <c r="G45" s="49"/>
@@ -9827,11 +9823,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="216"/>
-      <c r="B46" s="217"/>
-      <c r="C46" s="217"/>
-      <c r="D46" s="217"/>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="148"/>
+      <c r="B46" s="149"/>
+      <c r="C46" s="149"/>
+      <c r="D46" s="149"/>
       <c r="E46" s="34"/>
       <c r="F46" s="63"/>
       <c r="G46" s="50"/>
@@ -9839,11 +9835,11 @@
       <c r="I46" s="76"/>
       <c r="J46" s="76"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A47" s="215"/>
-      <c r="B47" s="214"/>
-      <c r="C47" s="214"/>
-      <c r="D47" s="214"/>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="147"/>
+      <c r="B47" s="146"/>
+      <c r="C47" s="146"/>
+      <c r="D47" s="146"/>
       <c r="E47" s="28"/>
       <c r="F47" s="60"/>
       <c r="G47" s="53"/>
@@ -9851,17 +9847,17 @@
       <c r="I47" s="32"/>
       <c r="J47" s="77"/>
     </row>
-    <row r="48" spans="1:12" s="39" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="205">
+    <row r="48" spans="1:12" s="39" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A48" s="137">
         <v>4</v>
       </c>
-      <c r="B48" s="206" t="s">
+      <c r="B48" s="138" t="s">
         <v>445</v>
       </c>
-      <c r="C48" s="206" t="s">
+      <c r="C48" s="138" t="s">
         <v>571</v>
       </c>
-      <c r="D48" s="206" t="s">
+      <c r="D48" s="138" t="s">
         <v>570</v>
       </c>
       <c r="E48" s="32" t="s">
@@ -9874,11 +9870,11 @@
       <c r="J48" s="40"/>
       <c r="L48" s="109"/>
     </row>
-    <row r="49" spans="1:12" s="39" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A49" s="218"/>
-      <c r="B49" s="219"/>
-      <c r="C49" s="219"/>
-      <c r="D49" s="219"/>
+    <row r="49" spans="1:12" s="39" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="150"/>
+      <c r="B49" s="151"/>
+      <c r="C49" s="151"/>
+      <c r="D49" s="151"/>
       <c r="E49" s="32"/>
       <c r="F49" s="58" t="s">
         <v>66</v>
@@ -9899,11 +9895,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="39" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="218"/>
-      <c r="B50" s="219"/>
-      <c r="C50" s="219"/>
-      <c r="D50" s="219"/>
+    <row r="50" spans="1:12" s="39" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="150"/>
+      <c r="B50" s="151"/>
+      <c r="C50" s="151"/>
+      <c r="D50" s="151"/>
       <c r="E50" s="32"/>
       <c r="F50" s="113"/>
       <c r="G50" s="49"/>
@@ -9918,11 +9914,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="218"/>
-      <c r="B51" s="219"/>
-      <c r="C51" s="219"/>
-      <c r="D51" s="219"/>
+    <row r="51" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="150"/>
+      <c r="B51" s="151"/>
+      <c r="C51" s="151"/>
+      <c r="D51" s="151"/>
       <c r="E51" s="32"/>
       <c r="F51" s="113"/>
       <c r="G51" s="49"/>
@@ -9931,41 +9927,41 @@
       <c r="J51" s="33"/>
       <c r="L51" s="131"/>
     </row>
-    <row r="52" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="218"/>
-      <c r="B52" s="219"/>
-      <c r="C52" s="219"/>
-      <c r="D52" s="219"/>
+    <row r="52" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="150"/>
+      <c r="B52" s="151"/>
+      <c r="C52" s="151"/>
+      <c r="D52" s="151"/>
       <c r="E52" s="32"/>
       <c r="F52" s="113"/>
       <c r="G52" s="49"/>
       <c r="H52" s="33"/>
-      <c r="I52" s="252" t="s">
+      <c r="I52" s="184" t="s">
         <v>582</v>
       </c>
       <c r="J52" s="33"/>
       <c r="L52" s="131"/>
     </row>
-    <row r="53" spans="1:12" s="39" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="218"/>
-      <c r="B53" s="219"/>
-      <c r="C53" s="219"/>
-      <c r="D53" s="219"/>
+    <row r="53" spans="1:12" s="39" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="150"/>
+      <c r="B53" s="151"/>
+      <c r="C53" s="151"/>
+      <c r="D53" s="151"/>
       <c r="E53" s="32"/>
       <c r="F53" s="113"/>
       <c r="G53" s="49"/>
       <c r="H53" s="33"/>
-      <c r="I53" s="254" t="s">
+      <c r="I53" s="186" t="s">
         <v>585</v>
       </c>
       <c r="J53" s="33"/>
       <c r="L53" s="131"/>
     </row>
-    <row r="54" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="218"/>
-      <c r="B54" s="219"/>
-      <c r="C54" s="219"/>
-      <c r="D54" s="219"/>
+    <row r="54" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="150"/>
+      <c r="B54" s="151"/>
+      <c r="C54" s="151"/>
+      <c r="D54" s="151"/>
       <c r="E54" s="32"/>
       <c r="F54" s="113"/>
       <c r="G54" s="49"/>
@@ -9974,11 +9970,11 @@
       <c r="J54" s="33"/>
       <c r="L54" s="131"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A55" s="220"/>
-      <c r="B55" s="217"/>
-      <c r="C55" s="217"/>
-      <c r="D55" s="217"/>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="152"/>
+      <c r="B55" s="149"/>
+      <c r="C55" s="149"/>
+      <c r="D55" s="149"/>
       <c r="E55" s="34"/>
       <c r="F55" s="64"/>
       <c r="G55" s="52"/>
@@ -9986,11 +9982,11 @@
       <c r="I55" s="35"/>
       <c r="J55" s="35"/>
     </row>
-    <row r="56" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="221"/>
-      <c r="B56" s="222"/>
-      <c r="C56" s="222"/>
-      <c r="D56" s="222"/>
+    <row r="56" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="153"/>
+      <c r="B56" s="154"/>
+      <c r="C56" s="154"/>
+      <c r="D56" s="154"/>
       <c r="E56" s="59"/>
       <c r="F56" s="60"/>
       <c r="G56" s="62"/>
@@ -9999,11 +9995,11 @@
       <c r="J56" s="65"/>
       <c r="L56" s="110"/>
     </row>
-    <row r="57" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="221"/>
-      <c r="B57" s="222"/>
-      <c r="C57" s="222"/>
-      <c r="D57" s="222"/>
+    <row r="57" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="153"/>
+      <c r="B57" s="154"/>
+      <c r="C57" s="154"/>
+      <c r="D57" s="154"/>
       <c r="E57" s="59"/>
       <c r="F57" s="94"/>
       <c r="G57" s="119"/>
@@ -10012,27 +10008,27 @@
       <c r="J57" s="65"/>
       <c r="L57" s="110"/>
     </row>
-    <row r="58" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="205">
+    <row r="58" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A58" s="137">
         <v>5</v>
       </c>
-      <c r="B58" s="206" t="s">
+      <c r="B58" s="138" t="s">
         <v>255</v>
       </c>
-      <c r="C58" s="206" t="s">
+      <c r="C58" s="138" t="s">
         <v>572</v>
       </c>
-      <c r="D58" s="206"/>
+      <c r="D58" s="138"/>
       <c r="E58" s="32" t="s">
         <v>356</v>
       </c>
-      <c r="F58" s="179" t="s">
+      <c r="F58" s="203" t="s">
         <v>66</v>
       </c>
-      <c r="G58" s="156" t="s">
+      <c r="G58" s="207" t="s">
         <v>358</v>
       </c>
-      <c r="H58" s="139" t="s">
+      <c r="H58" s="198" t="s">
         <v>179</v>
       </c>
       <c r="I58" s="33" t="s">
@@ -10045,15 +10041,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="64" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="223"/>
-      <c r="B59" s="219"/>
-      <c r="C59" s="219"/>
-      <c r="D59" s="219"/>
+    <row r="59" spans="1:12" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="155"/>
+      <c r="B59" s="151"/>
+      <c r="C59" s="151"/>
+      <c r="D59" s="151"/>
       <c r="E59" s="32"/>
-      <c r="F59" s="180"/>
-      <c r="G59" s="157"/>
-      <c r="H59" s="141"/>
+      <c r="F59" s="204"/>
+      <c r="G59" s="208"/>
+      <c r="H59" s="199"/>
       <c r="I59" s="88" t="s">
         <v>483</v>
       </c>
@@ -10062,11 +10058,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="61" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="223"/>
-      <c r="B60" s="219"/>
-      <c r="C60" s="224"/>
-      <c r="D60" s="224"/>
+    <row r="60" spans="1:12" s="61" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="155"/>
+      <c r="B60" s="151"/>
+      <c r="C60" s="156"/>
+      <c r="D60" s="156"/>
       <c r="E60" s="99"/>
       <c r="F60" s="97"/>
       <c r="G60" s="93"/>
@@ -10075,26 +10071,26 @@
       <c r="J60" s="96"/>
       <c r="L60" s="110"/>
     </row>
-    <row r="61" spans="1:12" s="61" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="176" t="s">
+    <row r="61" spans="1:12" s="61" customFormat="1" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="200" t="s">
         <v>446</v>
       </c>
-      <c r="B61" s="177"/>
-      <c r="C61" s="177"/>
-      <c r="D61" s="177"/>
-      <c r="E61" s="177"/>
-      <c r="F61" s="177"/>
-      <c r="G61" s="177"/>
-      <c r="H61" s="177"/>
-      <c r="I61" s="177"/>
-      <c r="J61" s="178"/>
+      <c r="B61" s="201"/>
+      <c r="C61" s="201"/>
+      <c r="D61" s="201"/>
+      <c r="E61" s="201"/>
+      <c r="F61" s="201"/>
+      <c r="G61" s="201"/>
+      <c r="H61" s="201"/>
+      <c r="I61" s="201"/>
+      <c r="J61" s="202"/>
       <c r="L61" s="110"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A62" s="216"/>
-      <c r="B62" s="217"/>
-      <c r="C62" s="217"/>
-      <c r="D62" s="217"/>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="148"/>
+      <c r="B62" s="149"/>
+      <c r="C62" s="149"/>
+      <c r="D62" s="149"/>
       <c r="E62" s="34"/>
       <c r="F62" s="56"/>
       <c r="G62" s="52"/>
@@ -10102,7 +10098,7 @@
       <c r="I62" s="35"/>
       <c r="J62" s="35"/>
     </row>
-    <row r="63" spans="1:12" s="87" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" s="87" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
         <v>184</v>
       </c>
@@ -10110,56 +10106,56 @@
       <c r="C63" s="85"/>
       <c r="D63" s="85"/>
       <c r="E63" s="85"/>
-      <c r="F63" s="148" t="s">
+      <c r="F63" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="G63" s="149"/>
+      <c r="G63" s="188"/>
       <c r="H63" s="86"/>
       <c r="I63" s="86"/>
       <c r="J63" s="86"/>
       <c r="L63" s="108"/>
     </row>
-    <row r="64" spans="1:12" s="42" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="212"/>
-      <c r="B64" s="225"/>
-      <c r="C64" s="225"/>
-      <c r="D64" s="225"/>
+    <row r="64" spans="1:12" s="42" customFormat="1" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="144"/>
+      <c r="B64" s="157"/>
+      <c r="C64" s="157"/>
+      <c r="D64" s="157"/>
       <c r="E64" s="41"/>
-      <c r="F64" s="168"/>
-      <c r="G64" s="169"/>
+      <c r="F64" s="219"/>
+      <c r="G64" s="220"/>
       <c r="H64" s="78"/>
       <c r="I64" s="78"/>
       <c r="J64" s="78"/>
       <c r="L64" s="112"/>
     </row>
-    <row r="65" spans="1:12" s="39" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="226">
+    <row r="65" spans="1:12" s="39" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="158">
         <v>1</v>
       </c>
-      <c r="B65" s="227" t="s">
+      <c r="B65" s="159" t="s">
         <v>181</v>
       </c>
-      <c r="C65" s="227" t="s">
+      <c r="C65" s="159" t="s">
         <v>573</v>
       </c>
-      <c r="D65" s="227" t="s">
+      <c r="D65" s="159" t="s">
         <v>142</v>
       </c>
       <c r="E65" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="F65" s="142"/>
-      <c r="G65" s="143"/>
+      <c r="F65" s="193"/>
+      <c r="G65" s="194"/>
       <c r="H65" s="32"/>
       <c r="I65" s="32"/>
       <c r="J65" s="32"/>
       <c r="L65" s="109"/>
     </row>
-    <row r="66" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A66" s="228"/>
-      <c r="B66" s="214"/>
-      <c r="C66" s="214"/>
-      <c r="D66" s="214"/>
+    <row r="66" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="160"/>
+      <c r="B66" s="146"/>
+      <c r="C66" s="146"/>
+      <c r="D66" s="146"/>
       <c r="E66" s="28"/>
       <c r="F66" s="58" t="s">
         <v>66</v>
@@ -10178,11 +10174,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="228"/>
-      <c r="B67" s="214"/>
-      <c r="C67" s="214"/>
-      <c r="D67" s="214"/>
+    <row r="67" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="160"/>
+      <c r="B67" s="146"/>
+      <c r="C67" s="146"/>
+      <c r="D67" s="146"/>
       <c r="E67" s="28"/>
       <c r="F67" s="58" t="s">
         <v>67</v>
@@ -10201,11 +10197,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="228"/>
-      <c r="B68" s="214"/>
-      <c r="C68" s="214"/>
-      <c r="D68" s="214"/>
+    <row r="68" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="160"/>
+      <c r="B68" s="146"/>
+      <c r="C68" s="146"/>
+      <c r="D68" s="146"/>
       <c r="E68" s="28"/>
       <c r="F68" s="58" t="s">
         <v>68</v>
@@ -10224,11 +10220,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="145" x14ac:dyDescent="0.35">
-      <c r="A69" s="228"/>
-      <c r="B69" s="214"/>
-      <c r="C69" s="214"/>
-      <c r="D69" s="214"/>
+    <row r="69" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="160"/>
+      <c r="B69" s="146"/>
+      <c r="C69" s="146"/>
+      <c r="D69" s="146"/>
       <c r="E69" s="28"/>
       <c r="F69" s="58" t="s">
         <v>69</v>
@@ -10249,11 +10245,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="228"/>
-      <c r="B70" s="214"/>
-      <c r="C70" s="214"/>
-      <c r="D70" s="214"/>
+    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="160"/>
+      <c r="B70" s="146"/>
+      <c r="C70" s="146"/>
+      <c r="D70" s="146"/>
       <c r="E70" s="28"/>
       <c r="F70" s="58" t="s">
         <v>70</v>
@@ -10274,11 +10270,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="174" x14ac:dyDescent="0.35">
-      <c r="A71" s="228"/>
-      <c r="B71" s="214"/>
-      <c r="C71" s="214"/>
-      <c r="D71" s="214"/>
+    <row r="71" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="160"/>
+      <c r="B71" s="146"/>
+      <c r="C71" s="146"/>
+      <c r="D71" s="146"/>
       <c r="E71" s="28"/>
       <c r="F71" s="58" t="s">
         <v>93</v>
@@ -10299,11 +10295,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="228"/>
-      <c r="B72" s="214"/>
-      <c r="C72" s="214"/>
-      <c r="D72" s="214"/>
+    <row r="72" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="160"/>
+      <c r="B72" s="146"/>
+      <c r="C72" s="146"/>
+      <c r="D72" s="146"/>
       <c r="E72" s="28"/>
       <c r="F72" s="58" t="s">
         <v>94</v>
@@ -10322,11 +10318,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A73" s="228"/>
-      <c r="B73" s="214"/>
-      <c r="C73" s="214"/>
-      <c r="D73" s="214"/>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="160"/>
+      <c r="B73" s="146"/>
+      <c r="C73" s="146"/>
+      <c r="D73" s="146"/>
       <c r="E73" s="28"/>
       <c r="F73" s="100"/>
       <c r="G73" s="101"/>
@@ -10334,25 +10330,25 @@
       <c r="I73" s="32"/>
       <c r="J73" s="32"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A74" s="228"/>
-      <c r="B74" s="214"/>
-      <c r="C74" s="214"/>
-      <c r="D74" s="214"/>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="160"/>
+      <c r="B74" s="146"/>
+      <c r="C74" s="146"/>
+      <c r="D74" s="146"/>
       <c r="E74" s="28"/>
-      <c r="F74" s="152" t="s">
+      <c r="F74" s="191" t="s">
         <v>145</v>
       </c>
-      <c r="G74" s="153"/>
+      <c r="G74" s="192"/>
       <c r="H74" s="32"/>
       <c r="I74" s="32"/>
       <c r="J74" s="32"/>
     </row>
-    <row r="75" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="228"/>
-      <c r="B75" s="214"/>
-      <c r="C75" s="214"/>
-      <c r="D75" s="214"/>
+    <row r="75" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A75" s="160"/>
+      <c r="B75" s="146"/>
+      <c r="C75" s="146"/>
+      <c r="D75" s="146"/>
       <c r="E75" s="28"/>
       <c r="F75" s="58" t="s">
         <v>66</v>
@@ -10371,11 +10367,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A76" s="228"/>
-      <c r="B76" s="214"/>
-      <c r="C76" s="214"/>
-      <c r="D76" s="214"/>
+    <row r="76" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A76" s="160"/>
+      <c r="B76" s="146"/>
+      <c r="C76" s="146"/>
+      <c r="D76" s="146"/>
       <c r="E76" s="28"/>
       <c r="F76" s="58" t="s">
         <v>67</v>
@@ -10394,11 +10390,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="228"/>
-      <c r="B77" s="214"/>
-      <c r="C77" s="214"/>
-      <c r="D77" s="214"/>
+    <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="160"/>
+      <c r="B77" s="146"/>
+      <c r="C77" s="146"/>
+      <c r="D77" s="146"/>
       <c r="E77" s="28"/>
       <c r="F77" s="58" t="s">
         <v>68</v>
@@ -10417,11 +10413,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="228"/>
-      <c r="B78" s="214"/>
-      <c r="C78" s="214"/>
-      <c r="D78" s="214"/>
+    <row r="78" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A78" s="160"/>
+      <c r="B78" s="146"/>
+      <c r="C78" s="146"/>
+      <c r="D78" s="146"/>
       <c r="E78" s="98"/>
       <c r="F78" s="58" t="s">
         <v>69</v>
@@ -10442,11 +10438,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A79" s="228"/>
-      <c r="B79" s="214"/>
-      <c r="C79" s="214"/>
-      <c r="D79" s="214"/>
+    <row r="79" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="160"/>
+      <c r="B79" s="146"/>
+      <c r="C79" s="146"/>
+      <c r="D79" s="146"/>
       <c r="E79" s="28"/>
       <c r="F79" s="58" t="s">
         <v>70</v>
@@ -10465,11 +10461,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A80" s="229"/>
-      <c r="B80" s="217"/>
-      <c r="C80" s="217"/>
-      <c r="D80" s="217"/>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="161"/>
+      <c r="B80" s="149"/>
+      <c r="C80" s="149"/>
+      <c r="D80" s="149"/>
       <c r="E80" s="34"/>
       <c r="F80" s="56"/>
       <c r="G80" s="52"/>
@@ -10477,11 +10473,11 @@
       <c r="I80" s="35"/>
       <c r="J80" s="35"/>
     </row>
-    <row r="81" spans="1:12" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="228"/>
-      <c r="B81" s="214"/>
-      <c r="C81" s="214"/>
-      <c r="D81" s="214"/>
+    <row r="81" spans="1:12" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="160"/>
+      <c r="B81" s="146"/>
+      <c r="C81" s="146"/>
+      <c r="D81" s="146"/>
       <c r="E81" s="28"/>
       <c r="F81" s="57"/>
       <c r="G81" s="53"/>
@@ -10489,34 +10485,34 @@
       <c r="I81" s="32"/>
       <c r="J81" s="32"/>
     </row>
-    <row r="82" spans="1:12" s="39" customFormat="1" ht="55.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="226">
+    <row r="82" spans="1:12" s="39" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A82" s="158">
         <v>2</v>
       </c>
-      <c r="B82" s="227" t="s">
+      <c r="B82" s="159" t="s">
         <v>447</v>
       </c>
-      <c r="C82" s="227" t="s">
+      <c r="C82" s="159" t="s">
         <v>106</v>
       </c>
-      <c r="D82" s="227" t="s">
+      <c r="D82" s="159" t="s">
         <v>570</v>
       </c>
       <c r="E82" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="F82" s="142"/>
-      <c r="G82" s="143"/>
+      <c r="F82" s="193"/>
+      <c r="G82" s="194"/>
       <c r="H82" s="32"/>
       <c r="I82" s="32"/>
       <c r="J82" s="32"/>
       <c r="L82" s="109"/>
     </row>
-    <row r="83" spans="1:12" ht="174" x14ac:dyDescent="0.35">
-      <c r="A83" s="215"/>
-      <c r="B83" s="214"/>
-      <c r="C83" s="214"/>
-      <c r="D83" s="214"/>
+    <row r="83" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="147"/>
+      <c r="B83" s="146"/>
+      <c r="C83" s="146"/>
+      <c r="D83" s="146"/>
       <c r="E83" s="28"/>
       <c r="F83" s="58" t="s">
         <v>66</v>
@@ -10535,11 +10531,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A84" s="215"/>
-      <c r="B84" s="214"/>
-      <c r="C84" s="214"/>
-      <c r="D84" s="214"/>
+    <row r="84" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="147"/>
+      <c r="B84" s="146"/>
+      <c r="C84" s="146"/>
+      <c r="D84" s="146"/>
       <c r="E84" s="28"/>
       <c r="F84" s="58" t="s">
         <v>67</v>
@@ -10558,11 +10554,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="215"/>
-      <c r="B85" s="214"/>
-      <c r="C85" s="214"/>
-      <c r="D85" s="214"/>
+    <row r="85" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="147"/>
+      <c r="B85" s="146"/>
+      <c r="C85" s="146"/>
+      <c r="D85" s="146"/>
       <c r="E85" s="28"/>
       <c r="F85" s="58" t="s">
         <v>68</v>
@@ -10581,11 +10577,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A86" s="215"/>
-      <c r="B86" s="214"/>
-      <c r="C86" s="214"/>
-      <c r="D86" s="214"/>
+    <row r="86" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="147"/>
+      <c r="B86" s="146"/>
+      <c r="C86" s="146"/>
+      <c r="D86" s="146"/>
       <c r="E86" s="28"/>
       <c r="F86" s="58" t="s">
         <v>298</v>
@@ -10606,11 +10602,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A87" s="216"/>
-      <c r="B87" s="217"/>
-      <c r="C87" s="217"/>
-      <c r="D87" s="217"/>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="148"/>
+      <c r="B87" s="149"/>
+      <c r="C87" s="149"/>
+      <c r="D87" s="149"/>
       <c r="E87" s="34"/>
       <c r="F87" s="63"/>
       <c r="G87" s="52"/>
@@ -10618,11 +10614,11 @@
       <c r="I87" s="35"/>
       <c r="J87" s="35"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A88" s="215"/>
-      <c r="B88" s="214"/>
-      <c r="C88" s="214"/>
-      <c r="D88" s="214"/>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="147"/>
+      <c r="B88" s="146"/>
+      <c r="C88" s="146"/>
+      <c r="D88" s="146"/>
       <c r="E88" s="28"/>
       <c r="F88" s="60"/>
       <c r="G88" s="53"/>
@@ -10630,29 +10626,29 @@
       <c r="I88" s="32"/>
       <c r="J88" s="32"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A89" s="215"/>
-      <c r="B89" s="214"/>
-      <c r="C89" s="214"/>
-      <c r="D89" s="214"/>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="147"/>
+      <c r="B89" s="146"/>
+      <c r="C89" s="146"/>
+      <c r="D89" s="146"/>
       <c r="E89" s="28"/>
-      <c r="F89" s="137"/>
-      <c r="G89" s="138"/>
+      <c r="F89" s="189"/>
+      <c r="G89" s="190"/>
       <c r="H89" s="32"/>
       <c r="I89" s="32"/>
       <c r="J89" s="32"/>
     </row>
-    <row r="90" spans="1:12" s="39" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A90" s="226">
+    <row r="90" spans="1:12" s="39" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A90" s="158">
         <v>3</v>
       </c>
-      <c r="B90" s="227" t="s">
+      <c r="B90" s="159" t="s">
         <v>445</v>
       </c>
-      <c r="C90" s="227" t="s">
+      <c r="C90" s="159" t="s">
         <v>107</v>
       </c>
-      <c r="D90" s="227" t="s">
+      <c r="D90" s="159" t="s">
         <v>570</v>
       </c>
       <c r="E90" s="32" t="s">
@@ -10677,11 +10673,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="39" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A91" s="218"/>
-      <c r="B91" s="219"/>
-      <c r="C91" s="219"/>
-      <c r="D91" s="219"/>
+    <row r="91" spans="1:12" s="39" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="150"/>
+      <c r="B91" s="151"/>
+      <c r="C91" s="151"/>
+      <c r="D91" s="151"/>
       <c r="E91" s="32"/>
       <c r="F91" s="58"/>
       <c r="G91" s="49"/>
@@ -10692,11 +10688,11 @@
       <c r="J91" s="33"/>
       <c r="L91" s="109"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A92" s="220"/>
-      <c r="B92" s="217"/>
-      <c r="C92" s="230"/>
-      <c r="D92" s="217"/>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="152"/>
+      <c r="B92" s="149"/>
+      <c r="C92" s="162"/>
+      <c r="D92" s="149"/>
       <c r="E92" s="35"/>
       <c r="F92" s="72"/>
       <c r="G92" s="52"/>
@@ -10704,11 +10700,11 @@
       <c r="I92" s="35"/>
       <c r="J92" s="35"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A93" s="218"/>
-      <c r="B93" s="214"/>
-      <c r="C93" s="231"/>
-      <c r="D93" s="214"/>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="150"/>
+      <c r="B93" s="146"/>
+      <c r="C93" s="163"/>
+      <c r="D93" s="146"/>
       <c r="E93" s="32"/>
       <c r="F93" s="120"/>
       <c r="G93" s="53"/>
@@ -10716,11 +10712,11 @@
       <c r="I93" s="32"/>
       <c r="J93" s="32"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A94" s="218"/>
-      <c r="B94" s="214"/>
-      <c r="C94" s="231"/>
-      <c r="D94" s="214"/>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="150"/>
+      <c r="B94" s="146"/>
+      <c r="C94" s="163"/>
+      <c r="D94" s="146"/>
       <c r="E94" s="32"/>
       <c r="F94" s="121"/>
       <c r="G94" s="119"/>
@@ -10728,17 +10724,17 @@
       <c r="I94" s="32"/>
       <c r="J94" s="32"/>
     </row>
-    <row r="95" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="226">
+    <row r="95" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="158">
         <v>4</v>
       </c>
-      <c r="B95" s="227" t="s">
+      <c r="B95" s="159" t="s">
         <v>255</v>
       </c>
-      <c r="C95" s="227" t="s">
+      <c r="C95" s="159" t="s">
         <v>106</v>
       </c>
-      <c r="D95" s="227" t="s">
+      <c r="D95" s="159" t="s">
         <v>570</v>
       </c>
       <c r="E95" s="32" t="s">
@@ -10759,11 +10755,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="232"/>
-      <c r="B96" s="233"/>
-      <c r="C96" s="233"/>
-      <c r="D96" s="233"/>
+    <row r="96" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="164"/>
+      <c r="B96" s="165"/>
+      <c r="C96" s="165"/>
+      <c r="D96" s="165"/>
       <c r="E96" s="66"/>
       <c r="F96" s="64"/>
       <c r="G96" s="69"/>
@@ -10772,11 +10768,11 @@
       <c r="J96" s="79"/>
       <c r="L96" s="110"/>
     </row>
-    <row r="97" spans="1:12" ht="9.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="215"/>
-      <c r="B97" s="214"/>
-      <c r="C97" s="214"/>
-      <c r="D97" s="214"/>
+    <row r="97" spans="1:12" ht="9.4499999999999993" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="147"/>
+      <c r="B97" s="146"/>
+      <c r="C97" s="146"/>
+      <c r="D97" s="146"/>
       <c r="E97" s="28"/>
       <c r="F97" s="57"/>
       <c r="G97" s="53"/>
@@ -10784,35 +10780,35 @@
       <c r="I97" s="32"/>
       <c r="J97" s="32"/>
     </row>
-    <row r="98" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A98" s="226">
+    <row r="98" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="158">
         <v>5</v>
       </c>
-      <c r="B98" s="227" t="s">
+      <c r="B98" s="159" t="s">
         <v>445</v>
       </c>
-      <c r="C98" s="227" t="s">
+      <c r="C98" s="159" t="s">
         <v>185</v>
       </c>
-      <c r="D98" s="227" t="s">
+      <c r="D98" s="159" t="s">
         <v>142</v>
       </c>
       <c r="E98" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F98" s="137"/>
-      <c r="G98" s="138"/>
+      <c r="F98" s="189"/>
+      <c r="G98" s="190"/>
       <c r="H98" s="32" t="s">
         <v>300</v>
       </c>
       <c r="I98" s="32"/>
       <c r="J98" s="32"/>
     </row>
-    <row r="99" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A99" s="215"/>
-      <c r="B99" s="214"/>
-      <c r="C99" s="214"/>
-      <c r="D99" s="214"/>
+    <row r="99" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="147"/>
+      <c r="B99" s="146"/>
+      <c r="C99" s="146"/>
+      <c r="D99" s="146"/>
       <c r="E99" s="28"/>
       <c r="F99" s="58" t="s">
         <v>66</v>
@@ -10831,11 +10827,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A100" s="215"/>
-      <c r="B100" s="214"/>
-      <c r="C100" s="214"/>
-      <c r="D100" s="214"/>
+    <row r="100" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A100" s="147"/>
+      <c r="B100" s="146"/>
+      <c r="C100" s="146"/>
+      <c r="D100" s="146"/>
       <c r="E100" s="28"/>
       <c r="F100" s="58" t="s">
         <v>67</v>
@@ -10854,11 +10850,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="215"/>
-      <c r="B101" s="214"/>
-      <c r="C101" s="214"/>
-      <c r="D101" s="214"/>
+    <row r="101" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A101" s="147"/>
+      <c r="B101" s="146"/>
+      <c r="C101" s="146"/>
+      <c r="D101" s="146"/>
       <c r="E101" s="28"/>
       <c r="F101" s="58" t="s">
         <v>68</v>
@@ -10879,11 +10875,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A102" s="215"/>
-      <c r="B102" s="214"/>
-      <c r="C102" s="214"/>
-      <c r="D102" s="214"/>
+    <row r="102" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="147"/>
+      <c r="B102" s="146"/>
+      <c r="C102" s="146"/>
+      <c r="D102" s="146"/>
       <c r="E102" s="28"/>
       <c r="F102" s="113"/>
       <c r="G102" s="49"/>
@@ -10893,11 +10889,11 @@
       <c r="I102" s="96"/>
       <c r="J102" s="33"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A103" s="215"/>
-      <c r="B103" s="214"/>
-      <c r="C103" s="214"/>
-      <c r="D103" s="214"/>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" s="147"/>
+      <c r="B103" s="146"/>
+      <c r="C103" s="146"/>
+      <c r="D103" s="146"/>
       <c r="E103" s="28"/>
       <c r="F103" s="60"/>
       <c r="G103" s="62"/>
@@ -10905,25 +10901,25 @@
       <c r="I103" s="65"/>
       <c r="J103" s="65"/>
     </row>
-    <row r="104" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="170" t="s">
+    <row r="104" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="195" t="s">
         <v>359</v>
       </c>
-      <c r="B104" s="171"/>
-      <c r="C104" s="171"/>
-      <c r="D104" s="171"/>
-      <c r="E104" s="171"/>
-      <c r="F104" s="171"/>
-      <c r="G104" s="171"/>
-      <c r="H104" s="171"/>
-      <c r="I104" s="171"/>
-      <c r="J104" s="172"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A105" s="216"/>
-      <c r="B105" s="217"/>
-      <c r="C105" s="217"/>
-      <c r="D105" s="217"/>
+      <c r="B104" s="221"/>
+      <c r="C104" s="221"/>
+      <c r="D104" s="221"/>
+      <c r="E104" s="221"/>
+      <c r="F104" s="221"/>
+      <c r="G104" s="221"/>
+      <c r="H104" s="221"/>
+      <c r="I104" s="221"/>
+      <c r="J104" s="222"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" s="148"/>
+      <c r="B105" s="149"/>
+      <c r="C105" s="149"/>
+      <c r="D105" s="149"/>
       <c r="E105" s="34"/>
       <c r="F105" s="56"/>
       <c r="G105" s="52"/>
@@ -10931,7 +10927,7 @@
       <c r="I105" s="35"/>
       <c r="J105" s="35"/>
     </row>
-    <row r="106" spans="1:12" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="89" t="s">
         <v>189</v>
       </c>
@@ -10939,19 +10935,19 @@
       <c r="C106" s="90"/>
       <c r="D106" s="90"/>
       <c r="E106" s="90"/>
-      <c r="F106" s="148" t="s">
+      <c r="F106" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="G106" s="149"/>
+      <c r="G106" s="188"/>
       <c r="H106" s="91"/>
       <c r="I106" s="91"/>
       <c r="J106" s="91"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A107" s="215"/>
-      <c r="B107" s="214"/>
-      <c r="C107" s="214"/>
-      <c r="D107" s="214"/>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" s="147"/>
+      <c r="B107" s="146"/>
+      <c r="C107" s="146"/>
+      <c r="D107" s="146"/>
       <c r="E107" s="28"/>
       <c r="F107" s="57"/>
       <c r="G107" s="53"/>
@@ -10959,36 +10955,36 @@
       <c r="I107" s="32"/>
       <c r="J107" s="32"/>
     </row>
-    <row r="108" spans="1:12" s="39" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="234">
+    <row r="108" spans="1:12" s="39" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="166">
         <v>1</v>
       </c>
-      <c r="B108" s="235" t="s">
+      <c r="B108" s="167" t="s">
         <v>181</v>
       </c>
-      <c r="C108" s="235" t="s">
+      <c r="C108" s="167" t="s">
         <v>568</v>
       </c>
-      <c r="D108" s="235" t="s">
+      <c r="D108" s="167" t="s">
         <v>142</v>
       </c>
       <c r="E108" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="F108" s="137" t="s">
+      <c r="F108" s="189" t="s">
         <v>178</v>
       </c>
-      <c r="G108" s="138"/>
+      <c r="G108" s="190"/>
       <c r="H108" s="32"/>
       <c r="I108" s="32"/>
       <c r="J108" s="32"/>
       <c r="L108" s="109"/>
     </row>
-    <row r="109" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A109" s="215"/>
-      <c r="B109" s="214"/>
-      <c r="C109" s="214"/>
-      <c r="D109" s="214"/>
+    <row r="109" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A109" s="147"/>
+      <c r="B109" s="146"/>
+      <c r="C109" s="146"/>
+      <c r="D109" s="146"/>
       <c r="E109" s="28"/>
       <c r="F109" s="58" t="s">
         <v>66</v>
@@ -11007,11 +11003,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A110" s="215"/>
-      <c r="B110" s="214"/>
-      <c r="C110" s="214"/>
-      <c r="D110" s="214"/>
+    <row r="110" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="147"/>
+      <c r="B110" s="146"/>
+      <c r="C110" s="146"/>
+      <c r="D110" s="146"/>
       <c r="E110" s="28"/>
       <c r="F110" s="58" t="s">
         <v>67</v>
@@ -11030,11 +11026,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A111" s="215"/>
-      <c r="B111" s="214"/>
-      <c r="C111" s="214"/>
-      <c r="D111" s="214"/>
+    <row r="111" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A111" s="147"/>
+      <c r="B111" s="146"/>
+      <c r="C111" s="146"/>
+      <c r="D111" s="146"/>
       <c r="E111" s="28"/>
       <c r="F111" s="58" t="s">
         <v>68</v>
@@ -11053,11 +11049,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="215"/>
-      <c r="B112" s="214"/>
-      <c r="C112" s="214"/>
-      <c r="D112" s="214"/>
+    <row r="112" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="147"/>
+      <c r="B112" s="146"/>
+      <c r="C112" s="146"/>
+      <c r="D112" s="146"/>
       <c r="E112" s="28"/>
       <c r="F112" s="58" t="s">
         <v>69</v>
@@ -11078,11 +11074,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="215"/>
-      <c r="B113" s="214"/>
-      <c r="C113" s="214"/>
-      <c r="D113" s="214"/>
+    <row r="113" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A113" s="147"/>
+      <c r="B113" s="146"/>
+      <c r="C113" s="146"/>
+      <c r="D113" s="146"/>
       <c r="E113" s="28"/>
       <c r="F113" s="58" t="s">
         <v>70</v>
@@ -11098,11 +11094,11 @@
       </c>
       <c r="J113" s="33"/>
     </row>
-    <row r="114" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A114" s="215"/>
-      <c r="B114" s="214"/>
-      <c r="C114" s="214"/>
-      <c r="D114" s="214"/>
+    <row r="114" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A114" s="147"/>
+      <c r="B114" s="146"/>
+      <c r="C114" s="146"/>
+      <c r="D114" s="146"/>
       <c r="E114" s="28"/>
       <c r="F114" s="58"/>
       <c r="G114" s="49"/>
@@ -11119,11 +11115,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A115" s="215"/>
-      <c r="B115" s="214"/>
-      <c r="C115" s="214"/>
-      <c r="D115" s="214"/>
+    <row r="115" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A115" s="147"/>
+      <c r="B115" s="146"/>
+      <c r="C115" s="146"/>
+      <c r="D115" s="146"/>
       <c r="E115" s="28"/>
       <c r="F115" s="58"/>
       <c r="G115" s="49"/>
@@ -11136,11 +11132,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A116" s="215"/>
-      <c r="B116" s="214"/>
-      <c r="C116" s="214"/>
-      <c r="D116" s="214"/>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" s="147"/>
+      <c r="B116" s="146"/>
+      <c r="C116" s="146"/>
+      <c r="D116" s="146"/>
       <c r="E116" s="28"/>
       <c r="F116" s="58"/>
       <c r="G116" s="49"/>
@@ -11148,11 +11144,11 @@
       <c r="I116" s="33"/>
       <c r="J116" s="33"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A117" s="215"/>
-      <c r="B117" s="214"/>
-      <c r="C117" s="214"/>
-      <c r="D117" s="214"/>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117" s="147"/>
+      <c r="B117" s="146"/>
+      <c r="C117" s="146"/>
+      <c r="D117" s="146"/>
       <c r="E117" s="28"/>
       <c r="F117" s="58"/>
       <c r="G117" s="49"/>
@@ -11160,11 +11156,11 @@
       <c r="I117" s="33"/>
       <c r="J117" s="33"/>
     </row>
-    <row r="118" spans="1:12" ht="174" x14ac:dyDescent="0.35">
-      <c r="A118" s="215"/>
-      <c r="B118" s="214"/>
-      <c r="C118" s="214"/>
-      <c r="D118" s="214"/>
+    <row r="118" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="147"/>
+      <c r="B118" s="146"/>
+      <c r="C118" s="146"/>
+      <c r="D118" s="146"/>
       <c r="E118" s="28"/>
       <c r="F118" s="58" t="s">
         <v>93</v>
@@ -11185,11 +11181,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A119" s="215"/>
-      <c r="B119" s="214"/>
-      <c r="C119" s="214"/>
-      <c r="D119" s="214"/>
+    <row r="119" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A119" s="147"/>
+      <c r="B119" s="146"/>
+      <c r="C119" s="146"/>
+      <c r="D119" s="146"/>
       <c r="E119" s="28"/>
       <c r="F119" s="58" t="s">
         <v>94</v>
@@ -11208,11 +11204,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A120" s="215"/>
-      <c r="B120" s="214"/>
-      <c r="C120" s="214"/>
-      <c r="D120" s="214"/>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A120" s="147"/>
+      <c r="B120" s="146"/>
+      <c r="C120" s="146"/>
+      <c r="D120" s="146"/>
       <c r="E120" s="28"/>
       <c r="F120" s="57"/>
       <c r="G120" s="53"/>
@@ -11220,25 +11216,25 @@
       <c r="I120" s="32"/>
       <c r="J120" s="32"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A121" s="215"/>
-      <c r="B121" s="214"/>
-      <c r="C121" s="214"/>
-      <c r="D121" s="214"/>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A121" s="147"/>
+      <c r="B121" s="146"/>
+      <c r="C121" s="146"/>
+      <c r="D121" s="146"/>
       <c r="E121" s="28"/>
-      <c r="F121" s="152" t="s">
+      <c r="F121" s="191" t="s">
         <v>236</v>
       </c>
-      <c r="G121" s="153"/>
+      <c r="G121" s="192"/>
       <c r="H121" s="32"/>
       <c r="I121" s="32"/>
       <c r="J121" s="32"/>
     </row>
-    <row r="122" spans="1:12" ht="203" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="215"/>
-      <c r="B122" s="214"/>
-      <c r="C122" s="214"/>
-      <c r="D122" s="214"/>
+    <row r="122" spans="1:12" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="147"/>
+      <c r="B122" s="146"/>
+      <c r="C122" s="146"/>
+      <c r="D122" s="146"/>
       <c r="E122" s="28"/>
       <c r="F122" s="58" t="s">
         <v>66</v>
@@ -11246,7 +11242,7 @@
       <c r="G122" s="49" t="s">
         <v>390</v>
       </c>
-      <c r="H122" s="173" t="s">
+      <c r="H122" s="223" t="s">
         <v>499</v>
       </c>
       <c r="I122" s="33"/>
@@ -11257,11 +11253,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A123" s="215"/>
-      <c r="B123" s="214"/>
-      <c r="C123" s="214"/>
-      <c r="D123" s="214"/>
+    <row r="123" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A123" s="147"/>
+      <c r="B123" s="146"/>
+      <c r="C123" s="146"/>
+      <c r="D123" s="146"/>
       <c r="E123" s="28"/>
       <c r="F123" s="58" t="s">
         <v>67</v>
@@ -11269,7 +11265,7 @@
       <c r="G123" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="H123" s="173"/>
+      <c r="H123" s="223"/>
       <c r="I123" s="33"/>
       <c r="J123" s="33" t="s">
         <v>502</v>
@@ -11278,11 +11274,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A124" s="215"/>
-      <c r="B124" s="214"/>
-      <c r="C124" s="214"/>
-      <c r="D124" s="214"/>
+    <row r="124" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A124" s="147"/>
+      <c r="B124" s="146"/>
+      <c r="C124" s="146"/>
+      <c r="D124" s="146"/>
       <c r="E124" s="28"/>
       <c r="F124" s="58" t="s">
         <v>68</v>
@@ -11290,7 +11286,7 @@
       <c r="G124" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="H124" s="173"/>
+      <c r="H124" s="223"/>
       <c r="I124" s="33"/>
       <c r="J124" s="33" t="s">
         <v>503</v>
@@ -11299,11 +11295,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A125" s="215"/>
-      <c r="B125" s="214"/>
-      <c r="C125" s="214"/>
-      <c r="D125" s="214"/>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A125" s="147"/>
+      <c r="B125" s="146"/>
+      <c r="C125" s="146"/>
+      <c r="D125" s="146"/>
       <c r="E125" s="28"/>
       <c r="F125" s="58" t="s">
         <v>69</v>
@@ -11311,15 +11307,15 @@
       <c r="G125" s="49" t="s">
         <v>334</v>
       </c>
-      <c r="H125" s="173"/>
+      <c r="H125" s="223"/>
       <c r="I125" s="33"/>
       <c r="J125" s="33"/>
     </row>
-    <row r="126" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A126" s="215"/>
-      <c r="B126" s="214"/>
-      <c r="C126" s="214"/>
-      <c r="D126" s="214"/>
+    <row r="126" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A126" s="147"/>
+      <c r="B126" s="146"/>
+      <c r="C126" s="146"/>
+      <c r="D126" s="146"/>
       <c r="E126" s="28"/>
       <c r="F126" s="58" t="s">
         <v>70</v>
@@ -11333,11 +11329,11 @@
       <c r="I126" s="33"/>
       <c r="J126" s="33"/>
     </row>
-    <row r="127" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="215"/>
-      <c r="B127" s="214"/>
-      <c r="C127" s="214"/>
-      <c r="D127" s="214"/>
+    <row r="127" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="147"/>
+      <c r="B127" s="146"/>
+      <c r="C127" s="146"/>
+      <c r="D127" s="146"/>
       <c r="E127" s="28"/>
       <c r="F127" s="58" t="s">
         <v>93</v>
@@ -11356,11 +11352,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A128" s="215"/>
-      <c r="B128" s="214"/>
-      <c r="C128" s="214"/>
-      <c r="D128" s="214"/>
+    <row r="128" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A128" s="147"/>
+      <c r="B128" s="146"/>
+      <c r="C128" s="146"/>
+      <c r="D128" s="146"/>
       <c r="E128" s="28"/>
       <c r="F128" s="58"/>
       <c r="G128" s="49"/>
@@ -11370,11 +11366,11 @@
       <c r="I128" s="33"/>
       <c r="J128" s="33"/>
     </row>
-    <row r="129" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A129" s="215"/>
-      <c r="B129" s="214"/>
-      <c r="C129" s="214"/>
-      <c r="D129" s="214"/>
+    <row r="129" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="147"/>
+      <c r="B129" s="146"/>
+      <c r="C129" s="146"/>
+      <c r="D129" s="146"/>
       <c r="E129" s="28"/>
       <c r="F129" s="58" t="s">
         <v>309</v>
@@ -11395,11 +11391,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A130" s="216"/>
-      <c r="B130" s="217"/>
-      <c r="C130" s="217"/>
-      <c r="D130" s="217"/>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A130" s="148"/>
+      <c r="B130" s="149"/>
+      <c r="C130" s="149"/>
+      <c r="D130" s="149"/>
       <c r="E130" s="34"/>
       <c r="F130" s="64"/>
       <c r="G130" s="52"/>
@@ -11407,11 +11403,11 @@
       <c r="I130" s="35"/>
       <c r="J130" s="35"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A131" s="215"/>
-      <c r="B131" s="214"/>
-      <c r="C131" s="214"/>
-      <c r="D131" s="214"/>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" s="147"/>
+      <c r="B131" s="146"/>
+      <c r="C131" s="146"/>
+      <c r="D131" s="146"/>
       <c r="E131" s="28"/>
       <c r="F131" s="57"/>
       <c r="G131" s="53"/>
@@ -11419,33 +11415,33 @@
       <c r="I131" s="32"/>
       <c r="J131" s="32"/>
     </row>
-    <row r="132" spans="1:12" ht="37" x14ac:dyDescent="0.35">
-      <c r="A132" s="236">
+    <row r="132" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+      <c r="A132" s="168">
         <v>2</v>
       </c>
-      <c r="B132" s="237" t="s">
+      <c r="B132" s="169" t="s">
         <v>181</v>
       </c>
-      <c r="C132" s="237" t="s">
+      <c r="C132" s="169" t="s">
         <v>569</v>
       </c>
-      <c r="D132" s="237"/>
+      <c r="D132" s="169"/>
       <c r="E132" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="F132" s="137" t="s">
+      <c r="F132" s="189" t="s">
         <v>238</v>
       </c>
-      <c r="G132" s="138"/>
+      <c r="G132" s="190"/>
       <c r="H132" s="32"/>
       <c r="I132" s="32"/>
       <c r="J132" s="32"/>
     </row>
-    <row r="133" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A133" s="215"/>
-      <c r="B133" s="214"/>
-      <c r="C133" s="214"/>
-      <c r="D133" s="214"/>
+    <row r="133" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A133" s="147"/>
+      <c r="B133" s="146"/>
+      <c r="C133" s="146"/>
+      <c r="D133" s="146"/>
       <c r="E133" s="28"/>
       <c r="F133" s="58" t="s">
         <v>66</v>
@@ -11466,11 +11462,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A134" s="215"/>
-      <c r="B134" s="214"/>
-      <c r="C134" s="214"/>
-      <c r="D134" s="214"/>
+    <row r="134" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A134" s="147"/>
+      <c r="B134" s="146"/>
+      <c r="C134" s="146"/>
+      <c r="D134" s="146"/>
       <c r="E134" s="28"/>
       <c r="F134" s="58" t="s">
         <v>67</v>
@@ -11491,11 +11487,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A135" s="215"/>
-      <c r="B135" s="214"/>
-      <c r="C135" s="214"/>
-      <c r="D135" s="214"/>
+    <row r="135" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A135" s="147"/>
+      <c r="B135" s="146"/>
+      <c r="C135" s="146"/>
+      <c r="D135" s="146"/>
       <c r="E135" s="28"/>
       <c r="F135" s="58" t="s">
         <v>68</v>
@@ -11516,11 +11512,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A136" s="215"/>
-      <c r="B136" s="214"/>
-      <c r="C136" s="214"/>
-      <c r="D136" s="214"/>
+    <row r="136" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A136" s="147"/>
+      <c r="B136" s="146"/>
+      <c r="C136" s="146"/>
+      <c r="D136" s="146"/>
       <c r="E136" s="28"/>
       <c r="F136" s="58" t="s">
         <v>69</v>
@@ -11539,11 +11535,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A137" s="215"/>
-      <c r="B137" s="214"/>
-      <c r="C137" s="214"/>
-      <c r="D137" s="214"/>
+    <row r="137" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A137" s="147"/>
+      <c r="B137" s="146"/>
+      <c r="C137" s="146"/>
+      <c r="D137" s="146"/>
       <c r="E137" s="28"/>
       <c r="F137" s="58" t="s">
         <v>70</v>
@@ -11564,11 +11560,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A138" s="216"/>
-      <c r="B138" s="217"/>
-      <c r="C138" s="217"/>
-      <c r="D138" s="217"/>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138" s="148"/>
+      <c r="B138" s="149"/>
+      <c r="C138" s="149"/>
+      <c r="D138" s="149"/>
       <c r="E138" s="34"/>
       <c r="F138" s="56"/>
       <c r="G138" s="52"/>
@@ -11576,11 +11572,11 @@
       <c r="I138" s="35"/>
       <c r="J138" s="35"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A139" s="215"/>
-      <c r="B139" s="214"/>
-      <c r="C139" s="214"/>
-      <c r="D139" s="214"/>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139" s="147"/>
+      <c r="B139" s="146"/>
+      <c r="C139" s="146"/>
+      <c r="D139" s="146"/>
       <c r="E139" s="28"/>
       <c r="F139" s="57"/>
       <c r="G139" s="53"/>
@@ -11588,29 +11584,29 @@
       <c r="I139" s="32"/>
       <c r="J139" s="32"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A140" s="215"/>
-      <c r="B140" s="214"/>
-      <c r="C140" s="214"/>
-      <c r="D140" s="214"/>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" s="147"/>
+      <c r="B140" s="146"/>
+      <c r="C140" s="146"/>
+      <c r="D140" s="146"/>
       <c r="E140" s="28"/>
-      <c r="F140" s="142" t="s">
+      <c r="F140" s="193" t="s">
         <v>251</v>
       </c>
-      <c r="G140" s="143"/>
+      <c r="G140" s="194"/>
       <c r="H140" s="32"/>
       <c r="I140" s="32"/>
       <c r="J140" s="32"/>
     </row>
-    <row r="141" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A141" s="218">
+    <row r="141" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A141" s="150">
         <v>3</v>
       </c>
-      <c r="B141" s="237"/>
-      <c r="C141" s="235" t="s">
+      <c r="B141" s="169"/>
+      <c r="C141" s="167" t="s">
         <v>571</v>
       </c>
-      <c r="D141" s="237"/>
+      <c r="D141" s="169"/>
       <c r="E141" s="28" t="s">
         <v>289</v>
       </c>
@@ -11633,11 +11629,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A142" s="218"/>
-      <c r="B142" s="222"/>
-      <c r="C142" s="219"/>
-      <c r="D142" s="222"/>
+    <row r="142" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A142" s="150"/>
+      <c r="B142" s="154"/>
+      <c r="C142" s="151"/>
+      <c r="D142" s="154"/>
       <c r="E142" s="28"/>
       <c r="F142" s="58"/>
       <c r="G142" s="53"/>
@@ -11649,11 +11645,11 @@
       </c>
       <c r="J142" s="33"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A143" s="220"/>
-      <c r="B143" s="217"/>
-      <c r="C143" s="230"/>
-      <c r="D143" s="217"/>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A143" s="152"/>
+      <c r="B143" s="149"/>
+      <c r="C143" s="162"/>
+      <c r="D143" s="149"/>
       <c r="E143" s="34"/>
       <c r="F143" s="64"/>
       <c r="G143" s="52"/>
@@ -11661,11 +11657,11 @@
       <c r="I143" s="35"/>
       <c r="J143" s="35"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A144" s="215"/>
-      <c r="B144" s="214"/>
-      <c r="C144" s="214"/>
-      <c r="D144" s="214"/>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144" s="147"/>
+      <c r="B144" s="146"/>
+      <c r="C144" s="146"/>
+      <c r="D144" s="146"/>
       <c r="E144" s="28"/>
       <c r="F144" s="57"/>
       <c r="G144" s="53"/>
@@ -11673,35 +11669,35 @@
       <c r="I144" s="32"/>
       <c r="J144" s="32"/>
     </row>
-    <row r="145" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="218">
+    <row r="145" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A145" s="150">
         <v>4</v>
       </c>
-      <c r="B145" s="235" t="s">
+      <c r="B145" s="167" t="s">
         <v>180</v>
       </c>
-      <c r="C145" s="235" t="s">
+      <c r="C145" s="167" t="s">
         <v>185</v>
       </c>
-      <c r="D145" s="235" t="s">
+      <c r="D145" s="167" t="s">
         <v>142</v>
       </c>
       <c r="E145" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="F145" s="142"/>
-      <c r="G145" s="143"/>
+      <c r="F145" s="193"/>
+      <c r="G145" s="194"/>
       <c r="H145" s="40" t="s">
         <v>402</v>
       </c>
       <c r="I145" s="40"/>
       <c r="J145" s="40"/>
     </row>
-    <row r="146" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A146" s="218"/>
-      <c r="B146" s="219"/>
-      <c r="C146" s="219"/>
-      <c r="D146" s="219"/>
+    <row r="146" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="150"/>
+      <c r="B146" s="151"/>
+      <c r="C146" s="151"/>
+      <c r="D146" s="151"/>
       <c r="E146" s="32"/>
       <c r="F146" s="58" t="s">
         <v>66</v>
@@ -11720,11 +11716,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A147" s="218"/>
-      <c r="B147" s="219"/>
-      <c r="C147" s="219"/>
-      <c r="D147" s="219"/>
+    <row r="147" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A147" s="150"/>
+      <c r="B147" s="151"/>
+      <c r="C147" s="151"/>
+      <c r="D147" s="151"/>
       <c r="E147" s="32"/>
       <c r="F147" s="58"/>
       <c r="G147" s="49"/>
@@ -11739,11 +11735,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A148" s="218"/>
-      <c r="B148" s="219"/>
-      <c r="C148" s="219"/>
-      <c r="D148" s="219"/>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A148" s="150"/>
+      <c r="B148" s="151"/>
+      <c r="C148" s="151"/>
+      <c r="D148" s="151"/>
       <c r="E148" s="32"/>
       <c r="F148" s="60"/>
       <c r="G148" s="53"/>
@@ -11751,25 +11747,25 @@
       <c r="I148" s="65"/>
       <c r="J148" s="32"/>
     </row>
-    <row r="149" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="170" t="s">
+    <row r="149" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="195" t="s">
         <v>359</v>
       </c>
-      <c r="B149" s="174"/>
-      <c r="C149" s="174"/>
-      <c r="D149" s="174"/>
-      <c r="E149" s="174"/>
-      <c r="F149" s="174"/>
-      <c r="G149" s="174"/>
-      <c r="H149" s="174"/>
-      <c r="I149" s="174"/>
-      <c r="J149" s="175"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A150" s="215"/>
-      <c r="B150" s="214"/>
-      <c r="C150" s="214"/>
-      <c r="D150" s="214"/>
+      <c r="B149" s="196"/>
+      <c r="C149" s="196"/>
+      <c r="D149" s="196"/>
+      <c r="E149" s="196"/>
+      <c r="F149" s="196"/>
+      <c r="G149" s="196"/>
+      <c r="H149" s="196"/>
+      <c r="I149" s="196"/>
+      <c r="J149" s="197"/>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A150" s="147"/>
+      <c r="B150" s="146"/>
+      <c r="C150" s="146"/>
+      <c r="D150" s="146"/>
       <c r="E150" s="28"/>
       <c r="F150" s="57"/>
       <c r="G150" s="53"/>
@@ -11777,7 +11773,7 @@
       <c r="I150" s="32"/>
       <c r="J150" s="32"/>
     </row>
-    <row r="151" spans="1:12" s="105" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" s="105" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="89" t="s">
         <v>239</v>
       </c>
@@ -11785,20 +11781,20 @@
       <c r="C151" s="90"/>
       <c r="D151" s="90"/>
       <c r="E151" s="103"/>
-      <c r="F151" s="166" t="s">
+      <c r="F151" s="217" t="s">
         <v>240</v>
       </c>
-      <c r="G151" s="167"/>
+      <c r="G151" s="218"/>
       <c r="H151" s="104"/>
       <c r="I151" s="104"/>
       <c r="J151" s="104"/>
       <c r="L151" s="109"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A152" s="215"/>
-      <c r="B152" s="214"/>
-      <c r="C152" s="214"/>
-      <c r="D152" s="214"/>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A152" s="147"/>
+      <c r="B152" s="146"/>
+      <c r="C152" s="146"/>
+      <c r="D152" s="146"/>
       <c r="E152" s="28"/>
       <c r="F152" s="57"/>
       <c r="G152" s="53"/>
@@ -11806,33 +11802,33 @@
       <c r="I152" s="32"/>
       <c r="J152" s="32"/>
     </row>
-    <row r="153" spans="1:12" ht="37" x14ac:dyDescent="0.35">
-      <c r="A153" s="238">
+    <row r="153" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+      <c r="A153" s="170">
         <v>1</v>
       </c>
-      <c r="B153" s="239" t="s">
+      <c r="B153" s="171" t="s">
         <v>181</v>
       </c>
-      <c r="C153" s="239" t="s">
+      <c r="C153" s="171" t="s">
         <v>574</v>
       </c>
-      <c r="D153" s="239" t="s">
+      <c r="D153" s="171" t="s">
         <v>142</v>
       </c>
       <c r="E153" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="F153" s="137"/>
-      <c r="G153" s="138"/>
+      <c r="F153" s="189"/>
+      <c r="G153" s="190"/>
       <c r="H153" s="32"/>
       <c r="I153" s="32"/>
       <c r="J153" s="32"/>
     </row>
-    <row r="154" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A154" s="215"/>
-      <c r="B154" s="214"/>
-      <c r="C154" s="214"/>
-      <c r="D154" s="214"/>
+    <row r="154" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A154" s="147"/>
+      <c r="B154" s="146"/>
+      <c r="C154" s="146"/>
+      <c r="D154" s="146"/>
       <c r="E154" s="28"/>
       <c r="F154" s="58" t="s">
         <v>66</v>
@@ -11851,11 +11847,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A155" s="215"/>
-      <c r="B155" s="214"/>
-      <c r="C155" s="214"/>
-      <c r="D155" s="214"/>
+    <row r="155" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="147"/>
+      <c r="B155" s="146"/>
+      <c r="C155" s="146"/>
+      <c r="D155" s="146"/>
       <c r="E155" s="28"/>
       <c r="F155" s="58" t="s">
         <v>67</v>
@@ -11874,11 +11870,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A156" s="215"/>
-      <c r="B156" s="214"/>
-      <c r="C156" s="214"/>
-      <c r="D156" s="214"/>
+    <row r="156" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A156" s="147"/>
+      <c r="B156" s="146"/>
+      <c r="C156" s="146"/>
+      <c r="D156" s="146"/>
       <c r="E156" s="28"/>
       <c r="F156" s="58" t="s">
         <v>68</v>
@@ -11897,11 +11893,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A157" s="215"/>
-      <c r="B157" s="214"/>
-      <c r="C157" s="214"/>
-      <c r="D157" s="214"/>
+    <row r="157" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A157" s="147"/>
+      <c r="B157" s="146"/>
+      <c r="C157" s="146"/>
+      <c r="D157" s="146"/>
       <c r="E157" s="28"/>
       <c r="F157" s="58" t="s">
         <v>69</v>
@@ -11922,11 +11918,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A158" s="215"/>
-      <c r="B158" s="214"/>
-      <c r="C158" s="214"/>
-      <c r="D158" s="214"/>
+    <row r="158" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="147"/>
+      <c r="B158" s="146"/>
+      <c r="C158" s="146"/>
+      <c r="D158" s="146"/>
       <c r="E158" s="28"/>
       <c r="F158" s="58" t="s">
         <v>70</v>
@@ -11945,11 +11941,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A159" s="215"/>
-      <c r="B159" s="214"/>
-      <c r="C159" s="214"/>
-      <c r="D159" s="214"/>
+    <row r="159" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A159" s="147"/>
+      <c r="B159" s="146"/>
+      <c r="C159" s="146"/>
+      <c r="D159" s="146"/>
       <c r="E159" s="28"/>
       <c r="F159" s="58" t="s">
         <v>93</v>
@@ -11968,11 +11964,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A160" s="215"/>
-      <c r="B160" s="214"/>
-      <c r="C160" s="214"/>
-      <c r="D160" s="214"/>
+    <row r="160" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A160" s="147"/>
+      <c r="B160" s="146"/>
+      <c r="C160" s="146"/>
+      <c r="D160" s="146"/>
       <c r="E160" s="28"/>
       <c r="F160" s="58" t="s">
         <v>94</v>
@@ -11991,11 +11987,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A161" s="215"/>
-      <c r="B161" s="214"/>
-      <c r="C161" s="214"/>
-      <c r="D161" s="214"/>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A161" s="147"/>
+      <c r="B161" s="146"/>
+      <c r="C161" s="146"/>
+      <c r="D161" s="146"/>
       <c r="E161" s="28"/>
       <c r="F161" s="57"/>
       <c r="G161" s="53"/>
@@ -12003,25 +11999,25 @@
       <c r="I161" s="32"/>
       <c r="J161" s="32"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A162" s="215"/>
-      <c r="B162" s="214"/>
-      <c r="C162" s="214"/>
-      <c r="D162" s="214"/>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A162" s="147"/>
+      <c r="B162" s="146"/>
+      <c r="C162" s="146"/>
+      <c r="D162" s="146"/>
       <c r="E162" s="28"/>
-      <c r="F162" s="150" t="s">
+      <c r="F162" s="205" t="s">
         <v>145</v>
       </c>
-      <c r="G162" s="151"/>
+      <c r="G162" s="206"/>
       <c r="H162" s="32"/>
       <c r="I162" s="32"/>
       <c r="J162" s="32"/>
     </row>
-    <row r="163" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A163" s="215"/>
-      <c r="B163" s="214"/>
-      <c r="C163" s="214"/>
-      <c r="D163" s="214"/>
+    <row r="163" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A163" s="147"/>
+      <c r="B163" s="146"/>
+      <c r="C163" s="146"/>
+      <c r="D163" s="146"/>
       <c r="E163" s="28"/>
       <c r="F163" s="58" t="s">
         <v>66</v>
@@ -12042,11 +12038,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A164" s="215"/>
-      <c r="B164" s="214"/>
-      <c r="C164" s="214"/>
-      <c r="D164" s="214"/>
+    <row r="164" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A164" s="147"/>
+      <c r="B164" s="146"/>
+      <c r="C164" s="146"/>
+      <c r="D164" s="146"/>
       <c r="E164" s="28"/>
       <c r="F164" s="58" t="s">
         <v>67</v>
@@ -12067,11 +12063,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A165" s="215"/>
-      <c r="B165" s="214"/>
-      <c r="C165" s="214"/>
-      <c r="D165" s="214"/>
+    <row r="165" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A165" s="147"/>
+      <c r="B165" s="146"/>
+      <c r="C165" s="146"/>
+      <c r="D165" s="146"/>
       <c r="E165" s="28"/>
       <c r="F165" s="58" t="s">
         <v>68</v>
@@ -12090,11 +12086,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A166" s="215"/>
-      <c r="B166" s="214"/>
-      <c r="C166" s="214"/>
-      <c r="D166" s="214"/>
+    <row r="166" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A166" s="147"/>
+      <c r="B166" s="146"/>
+      <c r="C166" s="146"/>
+      <c r="D166" s="146"/>
       <c r="E166" s="28"/>
       <c r="F166" s="58" t="s">
         <v>298</v>
@@ -12113,11 +12109,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A167" s="215"/>
-      <c r="B167" s="214"/>
-      <c r="C167" s="214"/>
-      <c r="D167" s="214"/>
+    <row r="167" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A167" s="147"/>
+      <c r="B167" s="146"/>
+      <c r="C167" s="146"/>
+      <c r="D167" s="146"/>
       <c r="E167" s="28"/>
       <c r="F167" s="58" t="s">
         <v>241</v>
@@ -12138,11 +12134,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A168" s="215"/>
-      <c r="B168" s="214"/>
-      <c r="C168" s="214"/>
-      <c r="D168" s="214"/>
+    <row r="168" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A168" s="147"/>
+      <c r="B168" s="146"/>
+      <c r="C168" s="146"/>
+      <c r="D168" s="146"/>
       <c r="E168" s="28"/>
       <c r="F168" s="58" t="s">
         <v>308</v>
@@ -12161,11 +12157,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A169" s="216"/>
-      <c r="B169" s="217"/>
-      <c r="C169" s="217"/>
-      <c r="D169" s="217"/>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A169" s="148"/>
+      <c r="B169" s="149"/>
+      <c r="C169" s="149"/>
+      <c r="D169" s="149"/>
       <c r="E169" s="34"/>
       <c r="F169" s="64"/>
       <c r="G169" s="52"/>
@@ -12173,11 +12169,11 @@
       <c r="I169" s="35"/>
       <c r="J169" s="35"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A170" s="215"/>
-      <c r="B170" s="214"/>
-      <c r="C170" s="214"/>
-      <c r="D170" s="214"/>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A170" s="147"/>
+      <c r="B170" s="146"/>
+      <c r="C170" s="146"/>
+      <c r="D170" s="146"/>
       <c r="E170" s="28"/>
       <c r="F170" s="57"/>
       <c r="G170" s="53"/>
@@ -12185,34 +12181,34 @@
       <c r="I170" s="32"/>
       <c r="J170" s="32"/>
     </row>
-    <row r="171" spans="1:12" s="39" customFormat="1" ht="37" x14ac:dyDescent="0.35">
-      <c r="A171" s="238">
+    <row r="171" spans="1:12" s="39" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A171" s="170">
         <v>2</v>
       </c>
-      <c r="B171" s="239" t="s">
+      <c r="B171" s="171" t="s">
         <v>181</v>
       </c>
-      <c r="C171" s="239" t="s">
+      <c r="C171" s="171" t="s">
         <v>243</v>
       </c>
-      <c r="D171" s="239"/>
+      <c r="D171" s="171"/>
       <c r="E171" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="F171" s="137" t="s">
+      <c r="F171" s="189" t="s">
         <v>238</v>
       </c>
-      <c r="G171" s="138"/>
+      <c r="G171" s="190"/>
       <c r="H171" s="32"/>
       <c r="I171" s="32"/>
       <c r="J171" s="32"/>
       <c r="L171" s="109"/>
     </row>
-    <row r="172" spans="1:12" ht="174" x14ac:dyDescent="0.35">
-      <c r="A172" s="215"/>
-      <c r="B172" s="214"/>
-      <c r="C172" s="214"/>
-      <c r="D172" s="214"/>
+    <row r="172" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A172" s="147"/>
+      <c r="B172" s="146"/>
+      <c r="C172" s="146"/>
+      <c r="D172" s="146"/>
       <c r="E172" s="28"/>
       <c r="F172" s="58" t="s">
         <v>66</v>
@@ -12231,11 +12227,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A173" s="215"/>
-      <c r="B173" s="214"/>
-      <c r="C173" s="214"/>
-      <c r="D173" s="214"/>
+    <row r="173" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A173" s="147"/>
+      <c r="B173" s="146"/>
+      <c r="C173" s="146"/>
+      <c r="D173" s="146"/>
       <c r="E173" s="28"/>
       <c r="F173" s="58" t="s">
         <v>67</v>
@@ -12254,11 +12250,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A174" s="215"/>
-      <c r="B174" s="214"/>
-      <c r="C174" s="214"/>
-      <c r="D174" s="214"/>
+    <row r="174" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A174" s="147"/>
+      <c r="B174" s="146"/>
+      <c r="C174" s="146"/>
+      <c r="D174" s="146"/>
       <c r="E174" s="28"/>
       <c r="F174" s="58"/>
       <c r="G174" s="49" t="s">
@@ -12275,11 +12271,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A175" s="215"/>
-      <c r="B175" s="214"/>
-      <c r="C175" s="214"/>
-      <c r="D175" s="214"/>
+    <row r="175" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A175" s="147"/>
+      <c r="B175" s="146"/>
+      <c r="C175" s="146"/>
+      <c r="D175" s="146"/>
       <c r="E175" s="28"/>
       <c r="F175" s="58" t="s">
         <v>69</v>
@@ -12300,11 +12296,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A176" s="216"/>
-      <c r="B176" s="217"/>
-      <c r="C176" s="217"/>
-      <c r="D176" s="217"/>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A176" s="148"/>
+      <c r="B176" s="149"/>
+      <c r="C176" s="149"/>
+      <c r="D176" s="149"/>
       <c r="E176" s="34"/>
       <c r="F176" s="64"/>
       <c r="G176" s="52"/>
@@ -12312,11 +12308,11 @@
       <c r="I176" s="35"/>
       <c r="J176" s="35"/>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A177" s="215"/>
-      <c r="B177" s="214"/>
-      <c r="C177" s="214"/>
-      <c r="D177" s="214"/>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A177" s="147"/>
+      <c r="B177" s="146"/>
+      <c r="C177" s="146"/>
+      <c r="D177" s="146"/>
       <c r="E177" s="28"/>
       <c r="F177" s="60"/>
       <c r="G177" s="53"/>
@@ -12324,29 +12320,29 @@
       <c r="I177" s="32"/>
       <c r="J177" s="32"/>
     </row>
-    <row r="178" spans="1:12" ht="37" x14ac:dyDescent="0.35">
-      <c r="A178" s="238">
+    <row r="178" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+      <c r="A178" s="170">
         <v>3</v>
       </c>
-      <c r="B178" s="240"/>
-      <c r="C178" s="239" t="s">
+      <c r="B178" s="172"/>
+      <c r="C178" s="171" t="s">
         <v>244</v>
       </c>
-      <c r="D178" s="214"/>
+      <c r="D178" s="146"/>
       <c r="E178" s="28"/>
-      <c r="F178" s="137" t="s">
+      <c r="F178" s="189" t="s">
         <v>252</v>
       </c>
-      <c r="G178" s="138"/>
+      <c r="G178" s="190"/>
       <c r="H178" s="32"/>
       <c r="I178" s="32"/>
       <c r="J178" s="32"/>
     </row>
-    <row r="179" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A179" s="218"/>
-      <c r="B179" s="214"/>
-      <c r="C179" s="231"/>
-      <c r="D179" s="214"/>
+    <row r="179" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A179" s="150"/>
+      <c r="B179" s="146"/>
+      <c r="C179" s="163"/>
+      <c r="D179" s="146"/>
       <c r="E179" s="28" t="s">
         <v>289</v>
       </c>
@@ -12369,11 +12365,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A180" s="215"/>
-      <c r="B180" s="214"/>
-      <c r="C180" s="231"/>
-      <c r="D180" s="214"/>
+    <row r="180" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A180" s="147"/>
+      <c r="B180" s="146"/>
+      <c r="C180" s="163"/>
+      <c r="D180" s="146"/>
       <c r="E180" s="28"/>
       <c r="F180" s="58"/>
       <c r="G180" s="49"/>
@@ -12383,11 +12379,11 @@
       <c r="I180" s="33"/>
       <c r="J180" s="33"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A181" s="216"/>
-      <c r="B181" s="217"/>
-      <c r="C181" s="230"/>
-      <c r="D181" s="217"/>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A181" s="148"/>
+      <c r="B181" s="149"/>
+      <c r="C181" s="162"/>
+      <c r="D181" s="149"/>
       <c r="E181" s="34"/>
       <c r="F181" s="123"/>
       <c r="G181" s="50"/>
@@ -12395,11 +12391,11 @@
       <c r="I181" s="76"/>
       <c r="J181" s="76"/>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A182" s="215"/>
-      <c r="B182" s="214"/>
-      <c r="C182" s="231"/>
-      <c r="D182" s="214"/>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A182" s="147"/>
+      <c r="B182" s="146"/>
+      <c r="C182" s="163"/>
+      <c r="D182" s="146"/>
       <c r="E182" s="28"/>
       <c r="F182" s="60"/>
       <c r="G182" s="53"/>
@@ -12407,24 +12403,24 @@
       <c r="I182" s="32"/>
       <c r="J182" s="32"/>
     </row>
-    <row r="183" spans="1:12" s="92" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="241">
+    <row r="183" spans="1:12" s="92" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="173">
         <v>4</v>
       </c>
-      <c r="B183" s="242" t="s">
+      <c r="B183" s="174" t="s">
         <v>448</v>
       </c>
-      <c r="C183" s="242" t="s">
+      <c r="C183" s="174" t="s">
         <v>450</v>
       </c>
-      <c r="D183" s="243" t="s">
+      <c r="D183" s="175" t="s">
         <v>449</v>
       </c>
       <c r="E183" s="37"/>
-      <c r="F183" s="154" t="s">
+      <c r="F183" s="229" t="s">
         <v>242</v>
       </c>
-      <c r="G183" s="155"/>
+      <c r="G183" s="230"/>
       <c r="H183" s="135" t="s">
         <v>314</v>
       </c>
@@ -12438,11 +12434,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="184" spans="1:12" s="92" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="241"/>
-      <c r="B184" s="242"/>
-      <c r="C184" s="242"/>
-      <c r="D184" s="243"/>
+    <row r="184" spans="1:12" s="92" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="173"/>
+      <c r="B184" s="174"/>
+      <c r="C184" s="174"/>
+      <c r="D184" s="175"/>
       <c r="E184" s="37"/>
       <c r="F184" s="133"/>
       <c r="G184" s="134"/>
@@ -12453,11 +12449,11 @@
       </c>
       <c r="L184" s="131"/>
     </row>
-    <row r="185" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="232"/>
-      <c r="B185" s="233"/>
-      <c r="C185" s="233"/>
-      <c r="D185" s="233"/>
+    <row r="185" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="164"/>
+      <c r="B185" s="165"/>
+      <c r="C185" s="165"/>
+      <c r="D185" s="165"/>
       <c r="E185" s="66"/>
       <c r="F185" s="67"/>
       <c r="G185" s="68"/>
@@ -12466,11 +12462,11 @@
       <c r="J185" s="79"/>
       <c r="L185" s="110"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A186" s="215"/>
-      <c r="B186" s="214"/>
-      <c r="C186" s="214"/>
-      <c r="D186" s="214"/>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A186" s="147"/>
+      <c r="B186" s="146"/>
+      <c r="C186" s="146"/>
+      <c r="D186" s="146"/>
       <c r="E186" s="28"/>
       <c r="F186" s="57"/>
       <c r="G186" s="53"/>
@@ -12478,33 +12474,33 @@
       <c r="I186" s="32"/>
       <c r="J186" s="32"/>
     </row>
-    <row r="187" spans="1:12" ht="55.5" x14ac:dyDescent="0.35">
-      <c r="A187" s="238">
+    <row r="187" spans="1:12" ht="54" x14ac:dyDescent="0.3">
+      <c r="A187" s="170">
         <v>5</v>
       </c>
-      <c r="B187" s="239" t="s">
+      <c r="B187" s="171" t="s">
         <v>180</v>
       </c>
-      <c r="C187" s="239" t="s">
+      <c r="C187" s="171" t="s">
         <v>245</v>
       </c>
-      <c r="D187" s="239" t="s">
+      <c r="D187" s="171" t="s">
         <v>142</v>
       </c>
       <c r="E187" s="32"/>
-      <c r="F187" s="137" t="s">
+      <c r="F187" s="189" t="s">
         <v>246</v>
       </c>
-      <c r="G187" s="138"/>
+      <c r="G187" s="190"/>
       <c r="H187" s="32"/>
       <c r="I187" s="32"/>
       <c r="J187" s="32"/>
     </row>
-    <row r="188" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A188" s="215"/>
-      <c r="B188" s="214"/>
-      <c r="C188" s="214"/>
-      <c r="D188" s="214"/>
+    <row r="188" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A188" s="147"/>
+      <c r="B188" s="146"/>
+      <c r="C188" s="146"/>
+      <c r="D188" s="146"/>
       <c r="E188" s="28"/>
       <c r="F188" s="58" t="s">
         <v>66</v>
@@ -12523,11 +12519,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A189" s="215"/>
-      <c r="B189" s="214"/>
-      <c r="C189" s="214"/>
-      <c r="D189" s="214"/>
+    <row r="189" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A189" s="147"/>
+      <c r="B189" s="146"/>
+      <c r="C189" s="146"/>
+      <c r="D189" s="146"/>
       <c r="E189" s="28"/>
       <c r="F189" s="58" t="s">
         <v>67</v>
@@ -12546,11 +12542,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A190" s="215"/>
-      <c r="B190" s="214"/>
-      <c r="C190" s="214"/>
-      <c r="D190" s="214"/>
+    <row r="190" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A190" s="147"/>
+      <c r="B190" s="146"/>
+      <c r="C190" s="146"/>
+      <c r="D190" s="146"/>
       <c r="E190" s="28"/>
       <c r="F190" s="58" t="s">
         <v>418</v>
@@ -12571,11 +12567,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A191" s="215"/>
-      <c r="B191" s="214"/>
-      <c r="C191" s="214"/>
-      <c r="D191" s="214"/>
+    <row r="191" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A191" s="147"/>
+      <c r="B191" s="146"/>
+      <c r="C191" s="146"/>
+      <c r="D191" s="146"/>
       <c r="E191" s="28"/>
       <c r="F191" s="58"/>
       <c r="G191" s="49"/>
@@ -12586,11 +12582,11 @@
       <c r="J191" s="33"/>
       <c r="L191" s="131"/>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A192" s="216"/>
-      <c r="B192" s="217"/>
-      <c r="C192" s="217"/>
-      <c r="D192" s="217"/>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A192" s="148"/>
+      <c r="B192" s="149"/>
+      <c r="C192" s="149"/>
+      <c r="D192" s="149"/>
       <c r="E192" s="34"/>
       <c r="F192" s="64"/>
       <c r="G192" s="52"/>
@@ -12598,11 +12594,11 @@
       <c r="I192" s="35"/>
       <c r="J192" s="35"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A193" s="215"/>
-      <c r="B193" s="214"/>
-      <c r="C193" s="214"/>
-      <c r="D193" s="214"/>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A193" s="147"/>
+      <c r="B193" s="146"/>
+      <c r="C193" s="146"/>
+      <c r="D193" s="146"/>
       <c r="E193" s="28"/>
       <c r="F193" s="57"/>
       <c r="G193" s="53"/>
@@ -12610,31 +12606,31 @@
       <c r="I193" s="32"/>
       <c r="J193" s="32"/>
     </row>
-    <row r="194" spans="1:13" ht="37" x14ac:dyDescent="0.35">
-      <c r="A194" s="241">
+    <row r="194" spans="1:13" ht="36" x14ac:dyDescent="0.3">
+      <c r="A194" s="173">
         <v>6</v>
       </c>
-      <c r="B194" s="240"/>
-      <c r="C194" s="240" t="s">
+      <c r="B194" s="172"/>
+      <c r="C194" s="172" t="s">
         <v>247</v>
       </c>
-      <c r="D194" s="240"/>
+      <c r="D194" s="172"/>
       <c r="E194" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="F194" s="137" t="s">
+      <c r="F194" s="189" t="s">
         <v>253</v>
       </c>
-      <c r="G194" s="138"/>
+      <c r="G194" s="190"/>
       <c r="H194" s="32"/>
       <c r="I194" s="32"/>
       <c r="J194" s="32"/>
     </row>
-    <row r="195" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A195" s="228"/>
-      <c r="B195" s="214"/>
-      <c r="C195" s="214"/>
-      <c r="D195" s="214"/>
+    <row r="195" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A195" s="160"/>
+      <c r="B195" s="146"/>
+      <c r="C195" s="146"/>
+      <c r="D195" s="146"/>
       <c r="E195" s="28"/>
       <c r="F195" s="58" t="s">
         <v>66</v>
@@ -12655,11 +12651,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A196" s="229"/>
-      <c r="B196" s="217"/>
-      <c r="C196" s="217"/>
-      <c r="D196" s="217"/>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A196" s="161"/>
+      <c r="B196" s="149"/>
+      <c r="C196" s="149"/>
+      <c r="D196" s="149"/>
       <c r="E196" s="34"/>
       <c r="F196" s="56"/>
       <c r="G196" s="52"/>
@@ -12667,11 +12663,11 @@
       <c r="I196" s="35"/>
       <c r="J196" s="35"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A197" s="215"/>
-      <c r="B197" s="214"/>
-      <c r="C197" s="214"/>
-      <c r="D197" s="214"/>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A197" s="147"/>
+      <c r="B197" s="146"/>
+      <c r="C197" s="146"/>
+      <c r="D197" s="146"/>
       <c r="E197" s="28"/>
       <c r="F197" s="57"/>
       <c r="G197" s="53"/>
@@ -12679,33 +12675,33 @@
       <c r="I197" s="32"/>
       <c r="J197" s="32"/>
     </row>
-    <row r="198" spans="1:13" ht="37" x14ac:dyDescent="0.35">
-      <c r="A198" s="241">
+    <row r="198" spans="1:13" ht="36" x14ac:dyDescent="0.3">
+      <c r="A198" s="173">
         <v>5</v>
       </c>
-      <c r="B198" s="240" t="s">
+      <c r="B198" s="172" t="s">
         <v>183</v>
       </c>
-      <c r="C198" s="240" t="s">
+      <c r="C198" s="172" t="s">
         <v>248</v>
       </c>
-      <c r="D198" s="240"/>
+      <c r="D198" s="172"/>
       <c r="E198" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="F198" s="146" t="s">
+      <c r="F198" s="227" t="s">
         <v>250</v>
       </c>
-      <c r="G198" s="147"/>
+      <c r="G198" s="228"/>
       <c r="H198" s="32"/>
       <c r="I198" s="32"/>
       <c r="J198" s="32"/>
     </row>
-    <row r="199" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A199" s="215"/>
-      <c r="B199" s="214"/>
-      <c r="C199" s="214"/>
-      <c r="D199" s="214"/>
+    <row r="199" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A199" s="147"/>
+      <c r="B199" s="146"/>
+      <c r="C199" s="146"/>
+      <c r="D199" s="146"/>
       <c r="E199" s="28"/>
       <c r="F199" s="58" t="s">
         <v>66</v>
@@ -12726,11 +12722,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A200" s="215"/>
-      <c r="B200" s="214"/>
-      <c r="C200" s="214"/>
-      <c r="D200" s="214"/>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A200" s="147"/>
+      <c r="B200" s="146"/>
+      <c r="C200" s="146"/>
+      <c r="D200" s="146"/>
       <c r="E200" s="28"/>
       <c r="F200" s="58"/>
       <c r="G200" s="49"/>
@@ -12740,11 +12736,11 @@
       <c r="L200" s="110"/>
       <c r="M200" s="61"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A201" s="216"/>
-      <c r="B201" s="217"/>
-      <c r="C201" s="217"/>
-      <c r="D201" s="217"/>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A201" s="148"/>
+      <c r="B201" s="149"/>
+      <c r="C201" s="149"/>
+      <c r="D201" s="149"/>
       <c r="E201" s="34"/>
       <c r="F201" s="56"/>
       <c r="G201" s="52"/>
@@ -12752,7 +12748,7 @@
       <c r="I201" s="35"/>
       <c r="J201" s="35"/>
     </row>
-    <row r="202" spans="1:13" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:13" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="89" t="s">
         <v>254</v>
       </c>
@@ -12760,19 +12756,19 @@
       <c r="C202" s="90"/>
       <c r="D202" s="90"/>
       <c r="E202" s="90"/>
-      <c r="F202" s="148" t="s">
+      <c r="F202" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="G202" s="149"/>
+      <c r="G202" s="188"/>
       <c r="H202" s="91"/>
       <c r="I202" s="91"/>
       <c r="J202" s="91"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A203" s="215"/>
-      <c r="B203" s="214"/>
-      <c r="C203" s="214"/>
-      <c r="D203" s="214"/>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A203" s="147"/>
+      <c r="B203" s="146"/>
+      <c r="C203" s="146"/>
+      <c r="D203" s="146"/>
       <c r="E203" s="28"/>
       <c r="F203" s="57"/>
       <c r="G203" s="53"/>
@@ -12780,33 +12776,33 @@
       <c r="I203" s="32"/>
       <c r="J203" s="32"/>
     </row>
-    <row r="204" spans="1:13" ht="87" x14ac:dyDescent="0.35">
-      <c r="A204" s="244">
+    <row r="204" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A204" s="176">
         <v>1</v>
       </c>
-      <c r="B204" s="245" t="s">
+      <c r="B204" s="177" t="s">
         <v>181</v>
       </c>
-      <c r="C204" s="245" t="s">
+      <c r="C204" s="177" t="s">
         <v>568</v>
       </c>
-      <c r="D204" s="245" t="s">
+      <c r="D204" s="177" t="s">
         <v>142</v>
       </c>
       <c r="E204" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="F204" s="137"/>
-      <c r="G204" s="138"/>
+      <c r="F204" s="189"/>
+      <c r="G204" s="190"/>
       <c r="H204" s="32"/>
       <c r="I204" s="32"/>
       <c r="J204" s="32"/>
     </row>
-    <row r="205" spans="1:13" ht="87" x14ac:dyDescent="0.35">
-      <c r="A205" s="215"/>
-      <c r="B205" s="214"/>
-      <c r="C205" s="214"/>
-      <c r="D205" s="214"/>
+    <row r="205" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A205" s="147"/>
+      <c r="B205" s="146"/>
+      <c r="C205" s="146"/>
+      <c r="D205" s="146"/>
       <c r="E205" s="28"/>
       <c r="F205" s="58" t="s">
         <v>66</v>
@@ -12825,11 +12821,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A206" s="215"/>
-      <c r="B206" s="214"/>
-      <c r="C206" s="214"/>
-      <c r="D206" s="214"/>
+    <row r="206" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A206" s="147"/>
+      <c r="B206" s="146"/>
+      <c r="C206" s="146"/>
+      <c r="D206" s="146"/>
       <c r="E206" s="28"/>
       <c r="F206" s="58" t="s">
         <v>67</v>
@@ -12848,11 +12844,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A207" s="215"/>
-      <c r="B207" s="214"/>
-      <c r="C207" s="214"/>
-      <c r="D207" s="214"/>
+    <row r="207" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A207" s="147"/>
+      <c r="B207" s="146"/>
+      <c r="C207" s="146"/>
+      <c r="D207" s="146"/>
       <c r="E207" s="28"/>
       <c r="F207" s="58" t="s">
         <v>68</v>
@@ -12871,11 +12867,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A208" s="215"/>
-      <c r="B208" s="214"/>
-      <c r="C208" s="214"/>
-      <c r="D208" s="214"/>
+    <row r="208" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A208" s="147"/>
+      <c r="B208" s="146"/>
+      <c r="C208" s="146"/>
+      <c r="D208" s="146"/>
       <c r="E208" s="28"/>
       <c r="F208" s="58" t="s">
         <v>69</v>
@@ -12896,11 +12892,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A209" s="215"/>
-      <c r="B209" s="214"/>
-      <c r="C209" s="214"/>
-      <c r="D209" s="214"/>
+    <row r="209" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A209" s="147"/>
+      <c r="B209" s="146"/>
+      <c r="C209" s="146"/>
+      <c r="D209" s="146"/>
       <c r="E209" s="28"/>
       <c r="F209" s="58" t="s">
         <v>70</v>
@@ -12921,11 +12917,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A210" s="215"/>
-      <c r="B210" s="214"/>
-      <c r="C210" s="214"/>
-      <c r="D210" s="214"/>
+    <row r="210" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A210" s="147"/>
+      <c r="B210" s="146"/>
+      <c r="C210" s="146"/>
+      <c r="D210" s="146"/>
       <c r="E210" s="28"/>
       <c r="F210" s="58" t="s">
         <v>93</v>
@@ -12944,11 +12940,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A211" s="215"/>
-      <c r="B211" s="214"/>
-      <c r="C211" s="214"/>
-      <c r="D211" s="214"/>
+    <row r="211" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A211" s="147"/>
+      <c r="B211" s="146"/>
+      <c r="C211" s="146"/>
+      <c r="D211" s="146"/>
       <c r="E211" s="28"/>
       <c r="F211" s="58" t="s">
         <v>94</v>
@@ -12967,11 +12963,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A212" s="215"/>
-      <c r="B212" s="214"/>
-      <c r="C212" s="214"/>
-      <c r="D212" s="214"/>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A212" s="147"/>
+      <c r="B212" s="146"/>
+      <c r="C212" s="146"/>
+      <c r="D212" s="146"/>
       <c r="E212" s="28"/>
       <c r="F212" s="57"/>
       <c r="G212" s="53"/>
@@ -12979,25 +12975,25 @@
       <c r="I212" s="32"/>
       <c r="J212" s="32"/>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A213" s="215"/>
-      <c r="B213" s="214"/>
-      <c r="C213" s="214"/>
-      <c r="D213" s="214"/>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A213" s="147"/>
+      <c r="B213" s="146"/>
+      <c r="C213" s="146"/>
+      <c r="D213" s="146"/>
       <c r="E213" s="28"/>
-      <c r="F213" s="150" t="s">
+      <c r="F213" s="205" t="s">
         <v>145</v>
       </c>
-      <c r="G213" s="151"/>
+      <c r="G213" s="206"/>
       <c r="H213" s="32"/>
       <c r="I213" s="32"/>
       <c r="J213" s="32"/>
     </row>
-    <row r="214" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A214" s="215"/>
-      <c r="B214" s="214"/>
-      <c r="C214" s="214"/>
-      <c r="D214" s="214"/>
+    <row r="214" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A214" s="147"/>
+      <c r="B214" s="146"/>
+      <c r="C214" s="146"/>
+      <c r="D214" s="146"/>
       <c r="E214" s="28"/>
       <c r="F214" s="58" t="s">
         <v>66</v>
@@ -13016,11 +13012,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A215" s="215"/>
-      <c r="B215" s="214"/>
-      <c r="C215" s="214"/>
-      <c r="D215" s="214"/>
+    <row r="215" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A215" s="147"/>
+      <c r="B215" s="146"/>
+      <c r="C215" s="146"/>
+      <c r="D215" s="146"/>
       <c r="E215" s="28"/>
       <c r="F215" s="58" t="s">
         <v>67</v>
@@ -13039,11 +13035,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A216" s="215"/>
-      <c r="B216" s="214"/>
-      <c r="C216" s="214"/>
-      <c r="D216" s="214"/>
+    <row r="216" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A216" s="147"/>
+      <c r="B216" s="146"/>
+      <c r="C216" s="146"/>
+      <c r="D216" s="146"/>
       <c r="E216" s="28"/>
       <c r="F216" s="58" t="s">
         <v>69</v>
@@ -13060,11 +13056,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A217" s="215"/>
-      <c r="B217" s="214"/>
-      <c r="C217" s="214"/>
-      <c r="D217" s="214"/>
+    <row r="217" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A217" s="147"/>
+      <c r="B217" s="146"/>
+      <c r="C217" s="146"/>
+      <c r="D217" s="146"/>
       <c r="E217" s="28"/>
       <c r="F217" s="58" t="s">
         <v>241</v>
@@ -13081,11 +13077,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A218" s="215"/>
-      <c r="B218" s="214"/>
-      <c r="C218" s="214"/>
-      <c r="D218" s="214"/>
+    <row r="218" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A218" s="147"/>
+      <c r="B218" s="146"/>
+      <c r="C218" s="146"/>
+      <c r="D218" s="146"/>
       <c r="E218" s="28"/>
       <c r="F218" s="58" t="s">
         <v>93</v>
@@ -13104,11 +13100,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A219" s="215"/>
-      <c r="B219" s="214"/>
-      <c r="C219" s="214"/>
-      <c r="D219" s="214"/>
+    <row r="219" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A219" s="147"/>
+      <c r="B219" s="146"/>
+      <c r="C219" s="146"/>
+      <c r="D219" s="146"/>
       <c r="E219" s="28"/>
       <c r="F219" s="58"/>
       <c r="G219" s="49"/>
@@ -13118,11 +13114,11 @@
       </c>
       <c r="J219" s="33"/>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A220" s="216"/>
-      <c r="B220" s="217"/>
-      <c r="C220" s="217"/>
-      <c r="D220" s="217"/>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A220" s="148"/>
+      <c r="B220" s="149"/>
+      <c r="C220" s="149"/>
+      <c r="D220" s="149"/>
       <c r="E220" s="34"/>
       <c r="F220" s="64"/>
       <c r="G220" s="50"/>
@@ -13130,11 +13126,11 @@
       <c r="I220" s="76"/>
       <c r="J220" s="76"/>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A221" s="215"/>
-      <c r="B221" s="214"/>
-      <c r="C221" s="214"/>
-      <c r="D221" s="214"/>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A221" s="147"/>
+      <c r="B221" s="146"/>
+      <c r="C221" s="146"/>
+      <c r="D221" s="146"/>
       <c r="E221" s="28"/>
       <c r="F221" s="57"/>
       <c r="G221" s="53"/>
@@ -13142,31 +13138,31 @@
       <c r="I221" s="32"/>
       <c r="J221" s="32"/>
     </row>
-    <row r="222" spans="1:12" ht="37" x14ac:dyDescent="0.35">
-      <c r="A222" s="244">
+    <row r="222" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+      <c r="A222" s="176">
         <v>2</v>
       </c>
-      <c r="B222" s="245" t="s">
+      <c r="B222" s="177" t="s">
         <v>181</v>
       </c>
-      <c r="C222" s="245" t="s">
+      <c r="C222" s="177" t="s">
         <v>243</v>
       </c>
-      <c r="D222" s="245"/>
+      <c r="D222" s="177"/>
       <c r="E222" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="F222" s="137"/>
-      <c r="G222" s="138"/>
+      <c r="F222" s="189"/>
+      <c r="G222" s="190"/>
       <c r="H222" s="32"/>
       <c r="I222" s="32"/>
       <c r="J222" s="40"/>
     </row>
-    <row r="223" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A223" s="215"/>
-      <c r="B223" s="214"/>
-      <c r="C223" s="214"/>
-      <c r="D223" s="214"/>
+    <row r="223" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A223" s="147"/>
+      <c r="B223" s="146"/>
+      <c r="C223" s="146"/>
+      <c r="D223" s="146"/>
       <c r="E223" s="28"/>
       <c r="F223" s="58" t="s">
         <v>66</v>
@@ -13185,11 +13181,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A224" s="215"/>
-      <c r="B224" s="214"/>
-      <c r="C224" s="214"/>
-      <c r="D224" s="214"/>
+    <row r="224" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A224" s="147"/>
+      <c r="B224" s="146"/>
+      <c r="C224" s="146"/>
+      <c r="D224" s="146"/>
       <c r="E224" s="28"/>
       <c r="F224" s="58" t="s">
         <v>67</v>
@@ -13208,11 +13204,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A225" s="215"/>
-      <c r="B225" s="214"/>
-      <c r="C225" s="214"/>
-      <c r="D225" s="214"/>
+    <row r="225" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A225" s="147"/>
+      <c r="B225" s="146"/>
+      <c r="C225" s="146"/>
+      <c r="D225" s="146"/>
       <c r="E225" s="28"/>
       <c r="F225" s="58" t="s">
         <v>68</v>
@@ -13233,11 +13229,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A226" s="216"/>
-      <c r="B226" s="217"/>
-      <c r="C226" s="217"/>
-      <c r="D226" s="217"/>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A226" s="148"/>
+      <c r="B226" s="149"/>
+      <c r="C226" s="149"/>
+      <c r="D226" s="149"/>
       <c r="E226" s="34"/>
       <c r="F226" s="102"/>
       <c r="G226" s="50"/>
@@ -13245,11 +13241,11 @@
       <c r="I226" s="76"/>
       <c r="J226" s="76"/>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A227" s="215"/>
-      <c r="B227" s="214"/>
-      <c r="C227" s="214"/>
-      <c r="D227" s="214"/>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A227" s="147"/>
+      <c r="B227" s="146"/>
+      <c r="C227" s="146"/>
+      <c r="D227" s="146"/>
       <c r="E227" s="28"/>
       <c r="F227" s="57"/>
       <c r="G227" s="53"/>
@@ -13257,27 +13253,27 @@
       <c r="I227" s="32"/>
       <c r="J227" s="32"/>
     </row>
-    <row r="228" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="246">
+    <row r="228" spans="1:12" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="178">
         <v>3</v>
       </c>
-      <c r="B228" s="247"/>
-      <c r="C228" s="247" t="s">
+      <c r="B228" s="179"/>
+      <c r="C228" s="179" t="s">
         <v>107</v>
       </c>
-      <c r="D228" s="247"/>
+      <c r="D228" s="179"/>
       <c r="E228" s="28"/>
-      <c r="F228" s="142"/>
-      <c r="G228" s="143"/>
+      <c r="F228" s="193"/>
+      <c r="G228" s="194"/>
       <c r="H228" s="32"/>
       <c r="I228" s="32"/>
       <c r="J228" s="32"/>
     </row>
-    <row r="229" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A229" s="215"/>
-      <c r="B229" s="214"/>
-      <c r="C229" s="214"/>
-      <c r="D229" s="214"/>
+    <row r="229" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A229" s="147"/>
+      <c r="B229" s="146"/>
+      <c r="C229" s="146"/>
+      <c r="D229" s="146"/>
       <c r="E229" s="28"/>
       <c r="F229" s="58" t="s">
         <v>66</v>
@@ -13298,11 +13294,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A230" s="216"/>
-      <c r="B230" s="217"/>
-      <c r="C230" s="217"/>
-      <c r="D230" s="217"/>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A230" s="148"/>
+      <c r="B230" s="149"/>
+      <c r="C230" s="149"/>
+      <c r="D230" s="149"/>
       <c r="E230" s="34"/>
       <c r="F230" s="63"/>
       <c r="G230" s="70"/>
@@ -13310,47 +13306,47 @@
       <c r="I230" s="35"/>
       <c r="J230" s="35"/>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A231" s="215"/>
-      <c r="B231" s="214"/>
-      <c r="C231" s="214"/>
-      <c r="D231" s="214"/>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A231" s="147"/>
+      <c r="B231" s="146"/>
+      <c r="C231" s="146"/>
+      <c r="D231" s="146"/>
       <c r="E231" s="28"/>
-      <c r="F231" s="144"/>
-      <c r="G231" s="145"/>
+      <c r="F231" s="225"/>
+      <c r="G231" s="226"/>
       <c r="H231" s="32"/>
       <c r="I231" s="32"/>
       <c r="J231" s="32"/>
     </row>
-    <row r="232" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A232" s="244">
+    <row r="232" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A232" s="176">
         <v>4</v>
       </c>
-      <c r="B232" s="245" t="s">
+      <c r="B232" s="177" t="s">
         <v>183</v>
       </c>
-      <c r="C232" s="245" t="s">
+      <c r="C232" s="177" t="s">
         <v>185</v>
       </c>
-      <c r="D232" s="245" t="s">
+      <c r="D232" s="177" t="s">
         <v>142</v>
       </c>
       <c r="E232" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="F232" s="137" t="s">
+      <c r="F232" s="189" t="s">
         <v>246</v>
       </c>
-      <c r="G232" s="138"/>
+      <c r="G232" s="190"/>
       <c r="H232" s="32"/>
       <c r="I232" s="32"/>
       <c r="J232" s="32"/>
     </row>
-    <row r="233" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A233" s="215"/>
-      <c r="B233" s="214"/>
-      <c r="C233" s="214"/>
-      <c r="D233" s="214"/>
+    <row r="233" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A233" s="147"/>
+      <c r="B233" s="146"/>
+      <c r="C233" s="146"/>
+      <c r="D233" s="146"/>
       <c r="E233" s="28"/>
       <c r="F233" s="58" t="s">
         <v>66</v>
@@ -13369,11 +13365,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A234" s="215"/>
-      <c r="B234" s="214"/>
-      <c r="C234" s="214"/>
-      <c r="D234" s="214"/>
+    <row r="234" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A234" s="147"/>
+      <c r="B234" s="146"/>
+      <c r="C234" s="146"/>
+      <c r="D234" s="146"/>
       <c r="E234" s="28"/>
       <c r="F234" s="58" t="s">
         <v>67</v>
@@ -13392,11 +13388,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A235" s="215"/>
-      <c r="B235" s="214"/>
-      <c r="C235" s="214"/>
-      <c r="D235" s="214"/>
+    <row r="235" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A235" s="147"/>
+      <c r="B235" s="146"/>
+      <c r="C235" s="146"/>
+      <c r="D235" s="146"/>
       <c r="E235" s="28"/>
       <c r="F235" s="58" t="s">
         <v>418</v>
@@ -13417,11 +13413,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A236" s="215"/>
-      <c r="B236" s="214"/>
-      <c r="C236" s="214"/>
-      <c r="D236" s="214"/>
+    <row r="236" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A236" s="147"/>
+      <c r="B236" s="146"/>
+      <c r="C236" s="146"/>
+      <c r="D236" s="146"/>
       <c r="E236" s="28"/>
       <c r="F236" s="58"/>
       <c r="G236" s="49"/>
@@ -13431,11 +13427,11 @@
       <c r="I236" s="96"/>
       <c r="J236" s="33"/>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A237" s="216"/>
-      <c r="B237" s="217"/>
-      <c r="C237" s="217"/>
-      <c r="D237" s="217"/>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A237" s="148"/>
+      <c r="B237" s="149"/>
+      <c r="C237" s="149"/>
+      <c r="D237" s="149"/>
       <c r="E237" s="34"/>
       <c r="F237" s="56"/>
       <c r="G237" s="52"/>
@@ -13443,11 +13439,11 @@
       <c r="I237" s="35"/>
       <c r="J237" s="35"/>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A238" s="216"/>
-      <c r="B238" s="217"/>
-      <c r="C238" s="217"/>
-      <c r="D238" s="217"/>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A238" s="148"/>
+      <c r="B238" s="149"/>
+      <c r="C238" s="149"/>
+      <c r="D238" s="149"/>
       <c r="E238" s="34"/>
       <c r="F238" s="56"/>
       <c r="G238" s="52"/>
@@ -13455,7 +13451,7 @@
       <c r="I238" s="35"/>
       <c r="J238" s="35"/>
     </row>
-    <row r="239" spans="1:12" s="128" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" s="128" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="89" t="s">
         <v>256</v>
       </c>
@@ -13463,20 +13459,20 @@
       <c r="C239" s="90"/>
       <c r="D239" s="90"/>
       <c r="E239" s="90"/>
-      <c r="F239" s="148" t="s">
+      <c r="F239" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="G239" s="149"/>
+      <c r="G239" s="188"/>
       <c r="H239" s="91"/>
       <c r="I239" s="91"/>
       <c r="J239" s="130"/>
       <c r="L239" s="129"/>
     </row>
-    <row r="240" spans="1:12" s="61" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="212"/>
-      <c r="B240" s="225"/>
-      <c r="C240" s="225"/>
-      <c r="D240" s="225"/>
+    <row r="240" spans="1:12" s="61" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="144"/>
+      <c r="B240" s="157"/>
+      <c r="C240" s="157"/>
+      <c r="D240" s="157"/>
       <c r="E240" s="41"/>
       <c r="F240" s="124"/>
       <c r="G240" s="125"/>
@@ -13485,11 +13481,11 @@
       <c r="J240" s="78"/>
       <c r="L240" s="110"/>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A241" s="215"/>
-      <c r="B241" s="214"/>
-      <c r="C241" s="214"/>
-      <c r="D241" s="214"/>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A241" s="147"/>
+      <c r="B241" s="146"/>
+      <c r="C241" s="146"/>
+      <c r="D241" s="146"/>
       <c r="E241" s="28"/>
       <c r="F241" s="117"/>
       <c r="G241" s="118"/>
@@ -13497,17 +13493,17 @@
       <c r="I241" s="40"/>
       <c r="J241" s="40"/>
     </row>
-    <row r="242" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A242" s="205">
+    <row r="242" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A242" s="137">
         <v>1</v>
       </c>
-      <c r="B242" s="206" t="s">
+      <c r="B242" s="138" t="s">
         <v>181</v>
       </c>
-      <c r="C242" s="206" t="s">
+      <c r="C242" s="138" t="s">
         <v>575</v>
       </c>
-      <c r="D242" s="206"/>
+      <c r="D242" s="138"/>
       <c r="E242" s="32" t="s">
         <v>435</v>
       </c>
@@ -13530,11 +13526,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A243" s="218"/>
-      <c r="B243" s="231"/>
-      <c r="C243" s="231"/>
-      <c r="D243" s="231"/>
+    <row r="243" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A243" s="150"/>
+      <c r="B243" s="163"/>
+      <c r="C243" s="163"/>
+      <c r="D243" s="163"/>
       <c r="E243" s="32"/>
       <c r="F243" s="58" t="s">
         <v>67</v>
@@ -13555,11 +13551,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A244" s="218"/>
-      <c r="B244" s="231"/>
-      <c r="C244" s="231"/>
-      <c r="D244" s="231"/>
+    <row r="244" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A244" s="150"/>
+      <c r="B244" s="163"/>
+      <c r="C244" s="163"/>
+      <c r="D244" s="163"/>
       <c r="E244" s="32"/>
       <c r="F244" s="58" t="s">
         <v>68</v>
@@ -13578,11 +13574,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A245" s="218"/>
-      <c r="B245" s="214"/>
-      <c r="C245" s="231"/>
-      <c r="D245" s="214"/>
+    <row r="245" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A245" s="150"/>
+      <c r="B245" s="146"/>
+      <c r="C245" s="163"/>
+      <c r="D245" s="146"/>
       <c r="E245" s="28"/>
       <c r="F245" s="58" t="s">
         <v>69</v>
@@ -13601,11 +13597,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A246" s="216"/>
-      <c r="B246" s="217"/>
-      <c r="C246" s="230"/>
-      <c r="D246" s="217"/>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A246" s="148"/>
+      <c r="B246" s="149"/>
+      <c r="C246" s="162"/>
+      <c r="D246" s="149"/>
       <c r="E246" s="34"/>
       <c r="F246" s="63"/>
       <c r="G246" s="50"/>
@@ -13613,11 +13609,11 @@
       <c r="I246" s="116"/>
       <c r="J246" s="76"/>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A247" s="215"/>
-      <c r="B247" s="214"/>
-      <c r="C247" s="214"/>
-      <c r="D247" s="214"/>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A247" s="147"/>
+      <c r="B247" s="146"/>
+      <c r="C247" s="146"/>
+      <c r="D247" s="146"/>
       <c r="E247" s="28"/>
       <c r="F247" s="114"/>
       <c r="G247" s="115"/>
@@ -13625,11 +13621,11 @@
       <c r="I247" s="40"/>
       <c r="J247" s="40"/>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A248" s="215"/>
-      <c r="B248" s="214"/>
-      <c r="C248" s="214"/>
-      <c r="D248" s="214"/>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A248" s="147"/>
+      <c r="B248" s="146"/>
+      <c r="C248" s="146"/>
+      <c r="D248" s="146"/>
       <c r="E248" s="28"/>
       <c r="F248" s="117"/>
       <c r="G248" s="118"/>
@@ -13637,15 +13633,15 @@
       <c r="I248" s="40"/>
       <c r="J248" s="40"/>
     </row>
-    <row r="249" spans="1:12" ht="37" x14ac:dyDescent="0.35">
-      <c r="A249" s="205">
+    <row r="249" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+      <c r="A249" s="137">
         <v>2</v>
       </c>
-      <c r="B249" s="248"/>
-      <c r="C249" s="248" t="s">
+      <c r="B249" s="180"/>
+      <c r="C249" s="180" t="s">
         <v>576</v>
       </c>
-      <c r="D249" s="248"/>
+      <c r="D249" s="180"/>
       <c r="E249" s="28" t="s">
         <v>443</v>
       </c>
@@ -13666,11 +13662,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A250" s="215"/>
-      <c r="B250" s="214"/>
-      <c r="C250" s="214"/>
-      <c r="D250" s="214"/>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A250" s="147"/>
+      <c r="B250" s="146"/>
+      <c r="C250" s="146"/>
+      <c r="D250" s="146"/>
       <c r="E250" s="28"/>
       <c r="F250" s="55"/>
       <c r="G250" s="49"/>
@@ -13678,11 +13674,11 @@
       <c r="I250" s="33"/>
       <c r="J250" s="33"/>
     </row>
-    <row r="251" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="216"/>
-      <c r="B251" s="217"/>
-      <c r="C251" s="217"/>
-      <c r="D251" s="217"/>
+    <row r="251" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="148"/>
+      <c r="B251" s="149"/>
+      <c r="C251" s="149"/>
+      <c r="D251" s="149"/>
       <c r="E251" s="34"/>
       <c r="F251" s="56"/>
       <c r="G251" s="52"/>
@@ -13690,7 +13686,7 @@
       <c r="I251" s="127"/>
       <c r="J251" s="35"/>
     </row>
-    <row r="252" spans="1:12" s="128" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" s="128" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="89" t="s">
         <v>273</v>
       </c>
@@ -13698,20 +13694,20 @@
       <c r="C252" s="90"/>
       <c r="D252" s="90"/>
       <c r="E252" s="90"/>
-      <c r="F252" s="148" t="s">
+      <c r="F252" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="G252" s="149"/>
+      <c r="G252" s="188"/>
       <c r="H252" s="91"/>
       <c r="I252" s="91"/>
       <c r="J252" s="91"/>
       <c r="L252" s="129"/>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A253" s="216"/>
-      <c r="B253" s="217"/>
-      <c r="C253" s="217"/>
-      <c r="D253" s="217"/>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A253" s="148"/>
+      <c r="B253" s="149"/>
+      <c r="C253" s="149"/>
+      <c r="D253" s="149"/>
       <c r="E253" s="34"/>
       <c r="F253" s="56"/>
       <c r="G253" s="52"/>
@@ -13719,11 +13715,11 @@
       <c r="I253" s="35"/>
       <c r="J253" s="35"/>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A254" s="216"/>
-      <c r="B254" s="217"/>
-      <c r="C254" s="217"/>
-      <c r="D254" s="217"/>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A254" s="148"/>
+      <c r="B254" s="149"/>
+      <c r="C254" s="149"/>
+      <c r="D254" s="149"/>
       <c r="E254" s="34"/>
       <c r="F254" s="56"/>
       <c r="G254" s="52"/>
@@ -13731,17 +13727,17 @@
       <c r="I254" s="35"/>
       <c r="J254" s="35"/>
     </row>
-    <row r="255" spans="1:12" ht="174" x14ac:dyDescent="0.35">
-      <c r="A255" s="205">
+    <row r="255" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A255" s="137">
         <v>1</v>
       </c>
-      <c r="B255" s="206" t="s">
+      <c r="B255" s="138" t="s">
         <v>181</v>
       </c>
-      <c r="C255" s="206" t="s">
+      <c r="C255" s="138" t="s">
         <v>517</v>
       </c>
-      <c r="D255" s="206"/>
+      <c r="D255" s="138"/>
       <c r="E255" s="32" t="s">
         <v>516</v>
       </c>
@@ -13764,11 +13760,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A256" s="218"/>
-      <c r="B256" s="231"/>
-      <c r="C256" s="231"/>
-      <c r="D256" s="231"/>
+    <row r="256" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A256" s="150"/>
+      <c r="B256" s="163"/>
+      <c r="C256" s="163"/>
+      <c r="D256" s="163"/>
       <c r="E256" s="32"/>
       <c r="F256" s="58" t="s">
         <v>67</v>
@@ -13789,11 +13785,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A257" s="218"/>
-      <c r="B257" s="231"/>
-      <c r="C257" s="231"/>
-      <c r="D257" s="231"/>
+    <row r="257" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A257" s="150"/>
+      <c r="B257" s="163"/>
+      <c r="C257" s="163"/>
+      <c r="D257" s="163"/>
       <c r="E257" s="32"/>
       <c r="F257" s="58" t="s">
         <v>68</v>
@@ -13812,11 +13808,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A258" s="218"/>
-      <c r="B258" s="214"/>
-      <c r="C258" s="231"/>
-      <c r="D258" s="214"/>
+    <row r="258" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A258" s="150"/>
+      <c r="B258" s="146"/>
+      <c r="C258" s="163"/>
+      <c r="D258" s="146"/>
       <c r="E258" s="28"/>
       <c r="F258" s="58" t="s">
         <v>69</v>
@@ -13835,11 +13831,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A259" s="216"/>
-      <c r="B259" s="217"/>
-      <c r="C259" s="230"/>
-      <c r="D259" s="217"/>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A259" s="148"/>
+      <c r="B259" s="149"/>
+      <c r="C259" s="162"/>
+      <c r="D259" s="149"/>
       <c r="E259" s="34"/>
       <c r="F259" s="63"/>
       <c r="G259" s="50"/>
@@ -13847,11 +13843,11 @@
       <c r="I259" s="116"/>
       <c r="J259" s="76"/>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A260" s="215"/>
-      <c r="B260" s="214"/>
-      <c r="C260" s="214"/>
-      <c r="D260" s="214"/>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A260" s="147"/>
+      <c r="B260" s="146"/>
+      <c r="C260" s="146"/>
+      <c r="D260" s="146"/>
       <c r="E260" s="28"/>
       <c r="F260" s="114"/>
       <c r="G260" s="115"/>
@@ -13859,11 +13855,11 @@
       <c r="I260" s="40"/>
       <c r="J260" s="40"/>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A261" s="215"/>
-      <c r="B261" s="214"/>
-      <c r="C261" s="214"/>
-      <c r="D261" s="214"/>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A261" s="147"/>
+      <c r="B261" s="146"/>
+      <c r="C261" s="146"/>
+      <c r="D261" s="146"/>
       <c r="E261" s="28"/>
       <c r="F261" s="117"/>
       <c r="G261" s="118"/>
@@ -13871,15 +13867,15 @@
       <c r="I261" s="40"/>
       <c r="J261" s="40"/>
     </row>
-    <row r="262" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A262" s="205">
+    <row r="262" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A262" s="137">
         <v>2</v>
       </c>
-      <c r="B262" s="248"/>
-      <c r="C262" s="248" t="s">
+      <c r="B262" s="180"/>
+      <c r="C262" s="180" t="s">
         <v>107</v>
       </c>
-      <c r="D262" s="248"/>
+      <c r="D262" s="180"/>
       <c r="E262" s="28" t="s">
         <v>443</v>
       </c>
@@ -13900,11 +13896,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A263" s="216"/>
-      <c r="B263" s="217"/>
-      <c r="C263" s="217"/>
-      <c r="D263" s="217"/>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A263" s="148"/>
+      <c r="B263" s="149"/>
+      <c r="C263" s="149"/>
+      <c r="D263" s="149"/>
       <c r="E263" s="34"/>
       <c r="F263" s="56"/>
       <c r="G263" s="52"/>
@@ -13912,11 +13908,11 @@
       <c r="I263" s="35"/>
       <c r="J263" s="35"/>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A264" s="216"/>
-      <c r="B264" s="217"/>
-      <c r="C264" s="217"/>
-      <c r="D264" s="217"/>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A264" s="148"/>
+      <c r="B264" s="149"/>
+      <c r="C264" s="149"/>
+      <c r="D264" s="149"/>
       <c r="E264" s="34"/>
       <c r="F264" s="56"/>
       <c r="G264" s="52"/>
@@ -13924,7 +13920,7 @@
       <c r="I264" s="35"/>
       <c r="J264" s="35"/>
     </row>
-    <row r="265" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="89" t="s">
         <v>274</v>
       </c>
@@ -13932,19 +13928,19 @@
       <c r="C265" s="90"/>
       <c r="D265" s="90"/>
       <c r="E265" s="90"/>
-      <c r="F265" s="148" t="s">
+      <c r="F265" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="G265" s="149"/>
+      <c r="G265" s="188"/>
       <c r="H265" s="91"/>
       <c r="I265" s="91"/>
       <c r="J265" s="91"/>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A266" s="216"/>
-      <c r="B266" s="217"/>
-      <c r="C266" s="217"/>
-      <c r="D266" s="217"/>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A266" s="148"/>
+      <c r="B266" s="149"/>
+      <c r="C266" s="149"/>
+      <c r="D266" s="149"/>
       <c r="E266" s="34"/>
       <c r="F266" s="56"/>
       <c r="G266" s="52"/>
@@ -13952,11 +13948,11 @@
       <c r="I266" s="35"/>
       <c r="J266" s="35"/>
     </row>
-    <row r="267" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A267" s="216"/>
-      <c r="B267" s="217"/>
-      <c r="C267" s="217"/>
-      <c r="D267" s="217"/>
+    <row r="267" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A267" s="148"/>
+      <c r="B267" s="149"/>
+      <c r="C267" s="149"/>
+      <c r="D267" s="149"/>
       <c r="E267" s="34"/>
       <c r="F267" s="56" t="s">
         <v>66</v>
@@ -13972,11 +13968,11 @@
       </c>
       <c r="J267" s="35"/>
     </row>
-    <row r="268" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A268" s="216"/>
-      <c r="B268" s="217"/>
-      <c r="C268" s="217"/>
-      <c r="D268" s="217"/>
+    <row r="268" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A268" s="148"/>
+      <c r="B268" s="149"/>
+      <c r="C268" s="149"/>
+      <c r="D268" s="149"/>
       <c r="E268" s="34"/>
       <c r="F268" s="56" t="s">
         <v>67</v>
@@ -13992,11 +13988,11 @@
       </c>
       <c r="J268" s="35"/>
     </row>
-    <row r="269" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A269" s="216"/>
-      <c r="B269" s="217"/>
-      <c r="C269" s="217"/>
-      <c r="D269" s="217"/>
+    <row r="269" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A269" s="148"/>
+      <c r="B269" s="149"/>
+      <c r="C269" s="149"/>
+      <c r="D269" s="149"/>
       <c r="E269" s="34"/>
       <c r="F269" s="56" t="s">
         <v>68</v>
@@ -14012,11 +14008,11 @@
       </c>
       <c r="J269" s="35"/>
     </row>
-    <row r="270" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A270" s="216"/>
-      <c r="B270" s="217"/>
-      <c r="C270" s="217"/>
-      <c r="D270" s="217"/>
+    <row r="270" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A270" s="148"/>
+      <c r="B270" s="149"/>
+      <c r="C270" s="149"/>
+      <c r="D270" s="149"/>
       <c r="E270" s="34"/>
       <c r="F270" s="56" t="s">
         <v>69</v>
@@ -14032,11 +14028,11 @@
       </c>
       <c r="J270" s="35"/>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A271" s="216"/>
-      <c r="B271" s="217"/>
-      <c r="C271" s="217"/>
-      <c r="D271" s="217"/>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A271" s="148"/>
+      <c r="B271" s="149"/>
+      <c r="C271" s="149"/>
+      <c r="D271" s="149"/>
       <c r="E271" s="34"/>
       <c r="F271" s="56"/>
       <c r="G271" s="52"/>
@@ -14044,7 +14040,7 @@
       <c r="I271" s="35"/>
       <c r="J271" s="35"/>
     </row>
-    <row r="272" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="89" t="s">
         <v>2</v>
       </c>
@@ -14052,19 +14048,19 @@
       <c r="C272" s="90"/>
       <c r="D272" s="90"/>
       <c r="E272" s="90"/>
-      <c r="F272" s="148" t="s">
+      <c r="F272" s="187" t="s">
         <v>76</v>
       </c>
-      <c r="G272" s="149"/>
+      <c r="G272" s="188"/>
       <c r="H272" s="91"/>
       <c r="I272" s="91"/>
       <c r="J272" s="91"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A273" s="216"/>
-      <c r="B273" s="217"/>
-      <c r="C273" s="217"/>
-      <c r="D273" s="217"/>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A273" s="148"/>
+      <c r="B273" s="149"/>
+      <c r="C273" s="149"/>
+      <c r="D273" s="149"/>
       <c r="E273" s="34"/>
       <c r="F273" s="56"/>
       <c r="G273" s="52"/>
@@ -14072,11 +14068,11 @@
       <c r="I273" s="35"/>
       <c r="J273" s="35"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A274" s="216"/>
-      <c r="B274" s="217"/>
-      <c r="C274" s="217"/>
-      <c r="D274" s="217"/>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A274" s="148"/>
+      <c r="B274" s="149"/>
+      <c r="C274" s="149"/>
+      <c r="D274" s="149"/>
       <c r="E274" s="34"/>
       <c r="F274" s="56" t="s">
         <v>66</v>
@@ -14088,11 +14084,11 @@
       <c r="I274" s="35"/>
       <c r="J274" s="35"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A275" s="216"/>
-      <c r="B275" s="217"/>
-      <c r="C275" s="217"/>
-      <c r="D275" s="217"/>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A275" s="148"/>
+      <c r="B275" s="149"/>
+      <c r="C275" s="149"/>
+      <c r="D275" s="149"/>
       <c r="E275" s="34"/>
       <c r="F275" s="56"/>
       <c r="G275" s="52" t="s">
@@ -14106,11 +14102,11 @@
       </c>
       <c r="J275" s="35"/>
     </row>
-    <row r="276" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A276" s="216"/>
-      <c r="B276" s="217"/>
-      <c r="C276" s="217"/>
-      <c r="D276" s="217"/>
+    <row r="276" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A276" s="148"/>
+      <c r="B276" s="149"/>
+      <c r="C276" s="149"/>
+      <c r="D276" s="149"/>
       <c r="E276" s="34"/>
       <c r="F276" s="56"/>
       <c r="G276" s="52"/>
@@ -14122,11 +14118,11 @@
       </c>
       <c r="J276" s="35"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A277" s="216"/>
-      <c r="B277" s="217"/>
-      <c r="C277" s="217"/>
-      <c r="D277" s="217"/>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A277" s="148"/>
+      <c r="B277" s="149"/>
+      <c r="C277" s="149"/>
+      <c r="D277" s="149"/>
       <c r="E277" s="34"/>
       <c r="F277" s="56"/>
       <c r="G277" s="52"/>
@@ -14138,11 +14134,11 @@
       </c>
       <c r="J277" s="35"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A278" s="216"/>
-      <c r="B278" s="217"/>
-      <c r="C278" s="217"/>
-      <c r="D278" s="217"/>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A278" s="148"/>
+      <c r="B278" s="149"/>
+      <c r="C278" s="149"/>
+      <c r="D278" s="149"/>
       <c r="E278" s="34"/>
       <c r="F278" s="56"/>
       <c r="G278" s="52" t="s">
@@ -14156,11 +14152,11 @@
       </c>
       <c r="J278" s="35"/>
     </row>
-    <row r="279" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A279" s="216"/>
-      <c r="B279" s="217"/>
-      <c r="C279" s="217"/>
-      <c r="D279" s="217"/>
+    <row r="279" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A279" s="148"/>
+      <c r="B279" s="149"/>
+      <c r="C279" s="149"/>
+      <c r="D279" s="149"/>
       <c r="E279" s="34"/>
       <c r="F279" s="56"/>
       <c r="G279" s="52"/>
@@ -14172,11 +14168,11 @@
       </c>
       <c r="J279" s="35"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A280" s="216"/>
-      <c r="B280" s="217"/>
-      <c r="C280" s="217"/>
-      <c r="D280" s="217"/>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A280" s="148"/>
+      <c r="B280" s="149"/>
+      <c r="C280" s="149"/>
+      <c r="D280" s="149"/>
       <c r="E280" s="34"/>
       <c r="F280" s="56"/>
       <c r="G280" s="52"/>
@@ -14188,11 +14184,11 @@
       </c>
       <c r="J280" s="35"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A281" s="216"/>
-      <c r="B281" s="217"/>
-      <c r="C281" s="217"/>
-      <c r="D281" s="217"/>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A281" s="148"/>
+      <c r="B281" s="149"/>
+      <c r="C281" s="149"/>
+      <c r="D281" s="149"/>
       <c r="E281" s="34"/>
       <c r="F281" s="56" t="s">
         <v>68</v>
@@ -14204,11 +14200,11 @@
       <c r="I281" s="35"/>
       <c r="J281" s="35"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A282" s="216"/>
-      <c r="B282" s="217"/>
-      <c r="C282" s="217"/>
-      <c r="D282" s="217"/>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A282" s="148"/>
+      <c r="B282" s="149"/>
+      <c r="C282" s="149"/>
+      <c r="D282" s="149"/>
       <c r="E282" s="34"/>
       <c r="F282" s="56"/>
       <c r="G282" s="52" t="s">
@@ -14222,11 +14218,11 @@
       </c>
       <c r="J282" s="35"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A283" s="216"/>
-      <c r="B283" s="217"/>
-      <c r="C283" s="217"/>
-      <c r="D283" s="217"/>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A283" s="148"/>
+      <c r="B283" s="149"/>
+      <c r="C283" s="149"/>
+      <c r="D283" s="149"/>
       <c r="E283" s="34"/>
       <c r="F283" s="56"/>
       <c r="G283" s="52" t="s">
@@ -14240,11 +14236,11 @@
       </c>
       <c r="J283" s="35"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A284" s="216"/>
-      <c r="B284" s="217"/>
-      <c r="C284" s="217"/>
-      <c r="D284" s="217"/>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A284" s="148"/>
+      <c r="B284" s="149"/>
+      <c r="C284" s="149"/>
+      <c r="D284" s="149"/>
       <c r="E284" s="34"/>
       <c r="F284" s="56"/>
       <c r="G284" s="52"/>
@@ -14252,11 +14248,11 @@
       <c r="I284" s="35"/>
       <c r="J284" s="35"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A285" s="216"/>
-      <c r="B285" s="217"/>
-      <c r="C285" s="217"/>
-      <c r="D285" s="217"/>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A285" s="148"/>
+      <c r="B285" s="149"/>
+      <c r="C285" s="149"/>
+      <c r="D285" s="149"/>
       <c r="E285" s="34"/>
       <c r="F285" s="56" t="s">
         <v>69</v>
@@ -14268,11 +14264,11 @@
       <c r="I285" s="35"/>
       <c r="J285" s="35"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A286" s="216"/>
-      <c r="B286" s="217"/>
-      <c r="C286" s="217"/>
-      <c r="D286" s="217"/>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A286" s="148"/>
+      <c r="B286" s="149"/>
+      <c r="C286" s="149"/>
+      <c r="D286" s="149"/>
       <c r="E286" s="34"/>
       <c r="F286" s="56"/>
       <c r="G286" s="52" t="s">
@@ -14286,11 +14282,11 @@
       </c>
       <c r="J286" s="35"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A287" s="216"/>
-      <c r="B287" s="217"/>
-      <c r="C287" s="217"/>
-      <c r="D287" s="217"/>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A287" s="148"/>
+      <c r="B287" s="149"/>
+      <c r="C287" s="149"/>
+      <c r="D287" s="149"/>
       <c r="E287" s="34"/>
       <c r="F287" s="56"/>
       <c r="G287" s="52"/>
@@ -14302,11 +14298,11 @@
       </c>
       <c r="J287" s="35"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A288" s="216"/>
-      <c r="B288" s="217"/>
-      <c r="C288" s="217"/>
-      <c r="D288" s="217"/>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A288" s="148"/>
+      <c r="B288" s="149"/>
+      <c r="C288" s="149"/>
+      <c r="D288" s="149"/>
       <c r="E288" s="34"/>
       <c r="F288" s="56"/>
       <c r="G288" s="52"/>
@@ -14314,11 +14310,11 @@
       <c r="I288" s="35"/>
       <c r="J288" s="35"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A289" s="216"/>
-      <c r="B289" s="217"/>
-      <c r="C289" s="217"/>
-      <c r="D289" s="217"/>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A289" s="148"/>
+      <c r="B289" s="149"/>
+      <c r="C289" s="149"/>
+      <c r="D289" s="149"/>
       <c r="E289" s="34"/>
       <c r="F289" s="56"/>
       <c r="G289" s="52"/>
@@ -14326,11 +14322,11 @@
       <c r="I289" s="35"/>
       <c r="J289" s="35"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A290" s="216"/>
-      <c r="B290" s="217"/>
-      <c r="C290" s="217"/>
-      <c r="D290" s="217"/>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A290" s="148"/>
+      <c r="B290" s="149"/>
+      <c r="C290" s="149"/>
+      <c r="D290" s="149"/>
       <c r="E290" s="34"/>
       <c r="F290" s="56"/>
       <c r="G290" s="52"/>
@@ -14338,11 +14334,11 @@
       <c r="I290" s="35"/>
       <c r="J290" s="35"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A291" s="216"/>
-      <c r="B291" s="217"/>
-      <c r="C291" s="217"/>
-      <c r="D291" s="217"/>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A291" s="148"/>
+      <c r="B291" s="149"/>
+      <c r="C291" s="149"/>
+      <c r="D291" s="149"/>
       <c r="E291" s="34"/>
       <c r="F291" s="56"/>
       <c r="G291" s="52" t="s">
@@ -14356,11 +14352,11 @@
       </c>
       <c r="J291" s="35"/>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A292" s="216"/>
-      <c r="B292" s="217"/>
-      <c r="C292" s="217"/>
-      <c r="D292" s="217"/>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A292" s="148"/>
+      <c r="B292" s="149"/>
+      <c r="C292" s="149"/>
+      <c r="D292" s="149"/>
       <c r="E292" s="34"/>
       <c r="F292" s="56"/>
       <c r="G292" s="52"/>
@@ -14372,11 +14368,11 @@
       </c>
       <c r="J292" s="35"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A293" s="216"/>
-      <c r="B293" s="217"/>
-      <c r="C293" s="217"/>
-      <c r="D293" s="217"/>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A293" s="148"/>
+      <c r="B293" s="149"/>
+      <c r="C293" s="149"/>
+      <c r="D293" s="149"/>
       <c r="E293" s="34"/>
       <c r="F293" s="56"/>
       <c r="G293" s="52"/>
@@ -14384,11 +14380,11 @@
       <c r="I293" s="35"/>
       <c r="J293" s="35"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A294" s="216"/>
-      <c r="B294" s="217"/>
-      <c r="C294" s="217"/>
-      <c r="D294" s="217"/>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A294" s="148"/>
+      <c r="B294" s="149"/>
+      <c r="C294" s="149"/>
+      <c r="D294" s="149"/>
       <c r="E294" s="34"/>
       <c r="F294" s="56"/>
       <c r="G294" s="52"/>
@@ -14396,7 +14392,7 @@
       <c r="I294" s="35"/>
       <c r="J294" s="35"/>
     </row>
-    <row r="295" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="89" t="s">
         <v>275</v>
       </c>
@@ -14404,19 +14400,19 @@
       <c r="C295" s="90"/>
       <c r="D295" s="90"/>
       <c r="E295" s="90"/>
-      <c r="F295" s="148" t="s">
+      <c r="F295" s="187" t="s">
         <v>77</v>
       </c>
-      <c r="G295" s="149"/>
+      <c r="G295" s="188"/>
       <c r="H295" s="91"/>
       <c r="I295" s="91"/>
       <c r="J295" s="91"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A296" s="216"/>
-      <c r="B296" s="217"/>
-      <c r="C296" s="217"/>
-      <c r="D296" s="217"/>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A296" s="148"/>
+      <c r="B296" s="149"/>
+      <c r="C296" s="149"/>
+      <c r="D296" s="149"/>
       <c r="E296" s="34"/>
       <c r="F296" s="56"/>
       <c r="G296" s="52"/>
@@ -14424,11 +14420,11 @@
       <c r="I296" s="35"/>
       <c r="J296" s="35"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A297" s="216"/>
-      <c r="B297" s="217"/>
-      <c r="C297" s="217"/>
-      <c r="D297" s="217"/>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A297" s="148"/>
+      <c r="B297" s="149"/>
+      <c r="C297" s="149"/>
+      <c r="D297" s="149"/>
       <c r="E297" s="34"/>
       <c r="F297" s="56"/>
       <c r="G297" s="52"/>
@@ -14438,25 +14434,7 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="F272:G272"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="F145:G145"/>
-    <mergeCell ref="F178:G178"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="A149:J149"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="F162:G162"/>
-    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="F140:G140"/>
     <mergeCell ref="F295:G295"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F8:G8"/>
@@ -14473,6 +14451,15 @@
     <mergeCell ref="H122:H125"/>
     <mergeCell ref="F232:G232"/>
     <mergeCell ref="I18:I21"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="G58:G59"/>
     <mergeCell ref="F228:G228"/>
     <mergeCell ref="F231:G231"/>
     <mergeCell ref="F194:G194"/>
@@ -14480,13 +14467,22 @@
     <mergeCell ref="F202:G202"/>
     <mergeCell ref="F204:G204"/>
     <mergeCell ref="F213:G213"/>
+    <mergeCell ref="F272:G272"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="A149:J149"/>
     <mergeCell ref="F222:G222"/>
     <mergeCell ref="F106:G106"/>
     <mergeCell ref="F121:G121"/>
     <mergeCell ref="F171:G171"/>
     <mergeCell ref="F187:G187"/>
     <mergeCell ref="F183:G183"/>
-    <mergeCell ref="F140:G140"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
@@ -14500,45 +14496,45 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133FACEA-C406-4EE9-B9D3-9A4E78E887A9}">
   <dimension ref="B2:J43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.7265625" style="29"/>
-    <col min="3" max="3" width="26.7265625" customWidth="1"/>
-    <col min="4" max="4" width="8.26953125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="29"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="22.36328125" customWidth="1"/>
-    <col min="8" max="8" width="39.26953125" customWidth="1"/>
-    <col min="9" max="10" width="8.7265625" style="29"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
+    <col min="8" max="8" width="39.21875" customWidth="1"/>
+    <col min="9" max="10" width="8.77734375" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="203" t="s">
+    <row r="2" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="253" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="203" t="s">
+      <c r="C2" s="253" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="203" t="s">
+      <c r="D2" s="253" t="s">
         <v>150</v>
       </c>
-      <c r="F2" s="202" t="s">
+      <c r="F2" s="252" t="s">
         <v>208</v>
       </c>
-      <c r="G2" s="202" t="s">
+      <c r="G2" s="252" t="s">
         <v>209</v>
       </c>
-      <c r="H2" s="202"/>
-      <c r="I2" s="202" t="s">
+      <c r="H2" s="252"/>
+      <c r="I2" s="252" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="202"/>
-    </row>
-    <row r="3" spans="2:10" s="3" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="204"/>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="F3" s="202"/>
+      <c r="J2" s="252"/>
+    </row>
+    <row r="3" spans="2:10" s="3" customFormat="1" ht="20.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="254"/>
+      <c r="C3" s="254"/>
+      <c r="D3" s="254"/>
+      <c r="F3" s="252"/>
       <c r="G3" s="31" t="s">
         <v>211</v>
       </c>
@@ -14552,7 +14548,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="30">
         <v>1</v>
       </c>
@@ -14574,7 +14570,7 @@
       </c>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="30">
         <f>B4+1</f>
         <v>2</v>
@@ -14595,7 +14591,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="30">
         <f t="shared" ref="B6:B20" si="0">B5+1</f>
         <v>3</v>
@@ -14616,7 +14612,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="30">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -14637,7 +14633,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="30">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -14658,7 +14654,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="30">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -14679,7 +14675,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="30">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -14700,7 +14696,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="30">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -14721,7 +14717,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="30">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -14738,7 +14734,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="30">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -14761,7 +14757,7 @@
       </c>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="30">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -14782,7 +14778,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="30">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -14803,7 +14799,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="30">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -14824,7 +14820,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="30">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -14845,7 +14841,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="30">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -14866,7 +14862,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -14887,7 +14883,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="30">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -14904,7 +14900,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F21" s="30">
         <v>3</v>
       </c>
@@ -14919,11 +14915,11 @@
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="G22" s="38"/>
       <c r="J22" s="46"/>
     </row>
-    <row r="23" spans="2:10" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="31" t="s">
         <v>208</v>
       </c>
@@ -14934,7 +14930,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="30">
         <v>1</v>
       </c>
@@ -14945,7 +14941,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="30">
         <f>B24+1</f>
         <v>2</v>
@@ -14957,7 +14953,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="30">
         <f t="shared" ref="B26:B28" si="1">B25+1</f>
         <v>3</v>
@@ -14969,7 +14965,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="30">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -14981,7 +14977,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -14993,7 +14989,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="2:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="31" t="s">
         <v>208</v>
       </c>
@@ -15004,7 +15000,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="30">
         <v>1</v>
       </c>
@@ -15013,7 +15009,7 @@
       </c>
       <c r="D31" s="30"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="30">
         <v>2</v>
       </c>
@@ -15022,7 +15018,7 @@
       </c>
       <c r="D32" s="30"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="30">
         <v>3</v>
       </c>
@@ -15031,7 +15027,7 @@
       </c>
       <c r="D33" s="30"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="30">
         <v>4</v>
       </c>
@@ -15040,7 +15036,7 @@
       </c>
       <c r="D34" s="30"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="30">
         <v>5</v>
       </c>
@@ -15049,12 +15045,12 @@
       </c>
       <c r="D35" s="30"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="30"/>
       <c r="C36" s="45"/>
       <c r="D36" s="30"/>
     </row>
-    <row r="38" spans="2:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="31" t="s">
         <v>208</v>
       </c>
@@ -15065,7 +15061,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="30">
         <v>1</v>
       </c>
@@ -15074,7 +15070,7 @@
       </c>
       <c r="D39" s="30"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="30">
         <v>2</v>
       </c>
@@ -15083,7 +15079,7 @@
       </c>
       <c r="D40" s="30"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="30">
         <v>3</v>
       </c>
@@ -15092,7 +15088,7 @@
       </c>
       <c r="D41" s="30"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="30">
         <v>4</v>
       </c>
@@ -15101,7 +15097,7 @@
       </c>
       <c r="D42" s="30"/>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="30"/>
       <c r="C43" s="45"/>
       <c r="D43" s="30"/>
@@ -15122,23 +15118,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9398260-1621-4A1E-904E-B99D19F48697}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="29"/>
-    <col min="2" max="2" width="37.6328125" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="29"/>
+    <col min="2" max="2" width="37.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="73" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="73" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>208</v>
       </c>
@@ -15146,22 +15142,22 @@
         <v>269</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>272</v>
       </c>
